--- a/artfynd/A 47952-2023 artfynd.xlsx
+++ b/artfynd/A 47952-2023 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117711408</v>
+        <v>117711523</v>
       </c>
       <c r="B10" t="n">
-        <v>78514</v>
+        <v>79069</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465002</v>
+        <v>465056</v>
       </c>
       <c r="R10" t="n">
-        <v>6823046</v>
+        <v>6823105</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117711475</v>
+        <v>117711657</v>
       </c>
       <c r="B11" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465003</v>
+        <v>465059</v>
       </c>
       <c r="R11" t="n">
-        <v>6823040</v>
+        <v>6822705</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117711771</v>
+        <v>117711732</v>
       </c>
       <c r="B12" t="n">
-        <v>78480</v>
+        <v>79606</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>229504</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465314</v>
+        <v>465042</v>
       </c>
       <c r="R12" t="n">
-        <v>6822659</v>
+        <v>6822859</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117711772</v>
+        <v>117711408</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465258</v>
+        <v>465002</v>
       </c>
       <c r="R13" t="n">
-        <v>6822696</v>
+        <v>6823046</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117711925</v>
+        <v>117711475</v>
       </c>
       <c r="B14" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465019</v>
+        <v>465003</v>
       </c>
       <c r="R14" t="n">
-        <v>6822782</v>
+        <v>6823040</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117711919</v>
+        <v>117711771</v>
       </c>
       <c r="B15" t="n">
         <v>78480</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465081</v>
+        <v>465314</v>
       </c>
       <c r="R15" t="n">
-        <v>6822777</v>
+        <v>6822659</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117711611</v>
+        <v>117711772</v>
       </c>
       <c r="B16" t="n">
-        <v>78506</v>
+        <v>78480</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465028</v>
+        <v>465258</v>
       </c>
       <c r="R16" t="n">
-        <v>6823122</v>
+        <v>6822696</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117711867</v>
+        <v>117711925</v>
       </c>
       <c r="B17" t="n">
         <v>78480</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464978</v>
+        <v>465019</v>
       </c>
       <c r="R17" t="n">
-        <v>6823101</v>
+        <v>6822782</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117711710</v>
+        <v>117711919</v>
       </c>
       <c r="B18" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465058</v>
+        <v>465081</v>
       </c>
       <c r="R18" t="n">
-        <v>6822707</v>
+        <v>6822777</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117711884</v>
+        <v>117711611</v>
       </c>
       <c r="B19" t="n">
-        <v>78480</v>
+        <v>78506</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465002</v>
+        <v>465028</v>
       </c>
       <c r="R19" t="n">
-        <v>6823138</v>
+        <v>6823122</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117711820</v>
+        <v>117711867</v>
       </c>
       <c r="B20" t="n">
         <v>78480</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465186</v>
+        <v>464978</v>
       </c>
       <c r="R20" t="n">
-        <v>6822793</v>
+        <v>6823101</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117711468</v>
+        <v>117711710</v>
       </c>
       <c r="B21" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465151</v>
+        <v>465058</v>
       </c>
       <c r="R21" t="n">
-        <v>6822788</v>
+        <v>6822707</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117711827</v>
+        <v>117711884</v>
       </c>
       <c r="B22" t="n">
         <v>78480</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465273</v>
+        <v>465002</v>
       </c>
       <c r="R22" t="n">
-        <v>6822555</v>
+        <v>6823138</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117711843</v>
+        <v>117711820</v>
       </c>
       <c r="B23" t="n">
         <v>78480</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465110</v>
+        <v>465186</v>
       </c>
       <c r="R23" t="n">
-        <v>6822717</v>
+        <v>6822793</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117711493</v>
+        <v>117711468</v>
       </c>
       <c r="B24" t="n">
         <v>79098</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465091</v>
+        <v>465151</v>
       </c>
       <c r="R24" t="n">
-        <v>6822828</v>
+        <v>6822788</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117711492</v>
+        <v>117711827</v>
       </c>
       <c r="B25" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465025</v>
+        <v>465273</v>
       </c>
       <c r="R25" t="n">
-        <v>6822860</v>
+        <v>6822555</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117711483</v>
+        <v>117711843</v>
       </c>
       <c r="B26" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464993</v>
+        <v>465110</v>
       </c>
       <c r="R26" t="n">
-        <v>6823209</v>
+        <v>6822717</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,7 +3225,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117711482</v>
+        <v>117711493</v>
       </c>
       <c r="B27" t="n">
         <v>79098</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464989</v>
+        <v>465091</v>
       </c>
       <c r="R27" t="n">
-        <v>6823223</v>
+        <v>6822828</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117711675</v>
+        <v>117711492</v>
       </c>
       <c r="B28" t="n">
-        <v>79561</v>
+        <v>79098</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465115</v>
+        <v>465025</v>
       </c>
       <c r="R28" t="n">
-        <v>6822797</v>
+        <v>6822860</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117711523</v>
+        <v>117711483</v>
       </c>
       <c r="B29" t="n">
-        <v>79069</v>
+        <v>79098</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465056</v>
+        <v>464993</v>
       </c>
       <c r="R29" t="n">
-        <v>6823105</v>
+        <v>6823209</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117711657</v>
+        <v>117711482</v>
       </c>
       <c r="B30" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465059</v>
+        <v>464989</v>
       </c>
       <c r="R30" t="n">
-        <v>6822705</v>
+        <v>6823223</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117711732</v>
+        <v>117711675</v>
       </c>
       <c r="B31" t="n">
-        <v>79606</v>
+        <v>79561</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229504</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465042</v>
+        <v>465115</v>
       </c>
       <c r="R31" t="n">
-        <v>6822859</v>
+        <v>6822797</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -5571,10 +5571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117711652</v>
+        <v>117711478</v>
       </c>
       <c r="B50" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465407</v>
+        <v>464943</v>
       </c>
       <c r="R50" t="n">
-        <v>6822454</v>
+        <v>6823108</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117711478</v>
+        <v>117711652</v>
       </c>
       <c r="B51" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5689,21 +5689,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464943</v>
+        <v>465407</v>
       </c>
       <c r="R51" t="n">
-        <v>6823108</v>
+        <v>6822454</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7212,10 +7212,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117711394</v>
+        <v>117711821</v>
       </c>
       <c r="B66" t="n">
-        <v>78514</v>
+        <v>78480</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7228,21 +7228,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465395</v>
+        <v>465185</v>
       </c>
       <c r="R66" t="n">
-        <v>6822489</v>
+        <v>6822757</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7314,10 +7314,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117711821</v>
+        <v>117711459</v>
       </c>
       <c r="B67" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7330,21 +7330,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465185</v>
+        <v>465193</v>
       </c>
       <c r="R67" t="n">
-        <v>6822757</v>
+        <v>6822569</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7416,10 +7416,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117711459</v>
+        <v>117711700</v>
       </c>
       <c r="B68" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7432,21 +7432,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465193</v>
+        <v>465104</v>
       </c>
       <c r="R68" t="n">
-        <v>6822569</v>
+        <v>6823045</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,10 +7518,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117711700</v>
+        <v>117711394</v>
       </c>
       <c r="B69" t="n">
-        <v>78216</v>
+        <v>78514</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7534,21 +7534,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7558,10 +7558,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465104</v>
+        <v>465395</v>
       </c>
       <c r="R69" t="n">
-        <v>6823045</v>
+        <v>6822489</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7836,10 +7836,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117711763</v>
+        <v>117711994</v>
       </c>
       <c r="B72" t="n">
-        <v>78480</v>
+        <v>78125</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7852,21 +7852,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465048</v>
+        <v>465054</v>
       </c>
       <c r="R72" t="n">
-        <v>6822660</v>
+        <v>6823006</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7938,10 +7938,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117711994</v>
+        <v>117711406</v>
       </c>
       <c r="B73" t="n">
-        <v>78125</v>
+        <v>78514</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7954,21 +7954,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7978,10 +7978,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465054</v>
+        <v>465008</v>
       </c>
       <c r="R73" t="n">
-        <v>6823006</v>
+        <v>6823044</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8040,10 +8040,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117711406</v>
+        <v>117711763</v>
       </c>
       <c r="B74" t="n">
-        <v>78514</v>
+        <v>78480</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8056,21 +8056,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8080,10 +8080,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465008</v>
+        <v>465048</v>
       </c>
       <c r="R74" t="n">
-        <v>6823044</v>
+        <v>6822660</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -15206,10 +15206,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>117711765</v>
+        <v>117711485</v>
       </c>
       <c r="B144" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15222,21 +15222,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15246,10 +15246,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>465105</v>
+        <v>465022</v>
       </c>
       <c r="R144" t="n">
-        <v>6822680</v>
+        <v>6823158</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15308,10 +15308,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>117711873</v>
+        <v>117711587</v>
       </c>
       <c r="B145" t="n">
-        <v>78480</v>
+        <v>79562</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15324,21 +15324,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15348,10 +15348,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>464912</v>
+        <v>465115</v>
       </c>
       <c r="R145" t="n">
-        <v>6823140</v>
+        <v>6822796</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15410,10 +15410,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>117711715</v>
+        <v>117711765</v>
       </c>
       <c r="B146" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15426,21 +15426,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15450,10 +15450,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>465052</v>
+        <v>465105</v>
       </c>
       <c r="R146" t="n">
-        <v>6823001</v>
+        <v>6822680</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15512,7 +15512,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>117711930</v>
+        <v>117711873</v>
       </c>
       <c r="B147" t="n">
         <v>78480</v>
@@ -15552,10 +15552,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>464991</v>
+        <v>464912</v>
       </c>
       <c r="R147" t="n">
-        <v>6822809</v>
+        <v>6823140</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15614,10 +15614,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>117711485</v>
+        <v>117711715</v>
       </c>
       <c r="B148" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15630,21 +15630,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15654,10 +15654,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>465022</v>
+        <v>465052</v>
       </c>
       <c r="R148" t="n">
-        <v>6823158</v>
+        <v>6823001</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15716,10 +15716,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>117711587</v>
+        <v>117711930</v>
       </c>
       <c r="B149" t="n">
-        <v>79562</v>
+        <v>78480</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15732,21 +15732,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15756,10 +15756,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>465115</v>
+        <v>464991</v>
       </c>
       <c r="R149" t="n">
-        <v>6822796</v>
+        <v>6822809</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15920,10 +15920,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>117711565</v>
+        <v>117711842</v>
       </c>
       <c r="B151" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15932,41 +15932,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>465115</v>
+        <v>465106</v>
       </c>
       <c r="R151" t="n">
-        <v>6822797</v>
+        <v>6822702</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16001,18 +15998,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -16031,10 +16022,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>117711555</v>
+        <v>117711769</v>
       </c>
       <c r="B152" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16043,41 +16034,38 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>464989</v>
+        <v>465379</v>
       </c>
       <c r="R152" t="n">
-        <v>6822826</v>
+        <v>6822539</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16112,18 +16100,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>På rönn</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16142,10 +16124,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>117711566</v>
+        <v>117711895</v>
       </c>
       <c r="B153" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16154,41 +16136,38 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>465130</v>
+        <v>465019</v>
       </c>
       <c r="R153" t="n">
-        <v>6822768</v>
+        <v>6822976</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16223,18 +16202,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -16253,10 +16226,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>117711397</v>
+        <v>117711788</v>
       </c>
       <c r="B154" t="n">
-        <v>78514</v>
+        <v>78480</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16269,21 +16242,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16293,10 +16266,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>465229</v>
+        <v>465095</v>
       </c>
       <c r="R154" t="n">
-        <v>6822789</v>
+        <v>6823035</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16355,7 +16328,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>117711842</v>
+        <v>117711868</v>
       </c>
       <c r="B155" t="n">
         <v>78480</v>
@@ -16395,10 +16368,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>465106</v>
+        <v>464976</v>
       </c>
       <c r="R155" t="n">
-        <v>6822702</v>
+        <v>6823119</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16457,7 +16430,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>117711769</v>
+        <v>117711845</v>
       </c>
       <c r="B156" t="n">
         <v>78480</v>
@@ -16497,10 +16470,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>465379</v>
+        <v>465139</v>
       </c>
       <c r="R156" t="n">
-        <v>6822539</v>
+        <v>6822785</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16559,7 +16532,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>117711895</v>
+        <v>117711736</v>
       </c>
       <c r="B157" t="n">
         <v>78480</v>
@@ -16593,16 +16566,19 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>465019</v>
+        <v>465029</v>
       </c>
       <c r="R157" t="n">
-        <v>6822976</v>
+        <v>6823165</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16637,12 +16613,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -16661,7 +16643,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>117711788</v>
+        <v>117711909</v>
       </c>
       <c r="B158" t="n">
         <v>78480</v>
@@ -16701,10 +16683,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>465095</v>
+        <v>465054</v>
       </c>
       <c r="R158" t="n">
-        <v>6823035</v>
+        <v>6822855</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16763,10 +16745,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>117711868</v>
+        <v>117711608</v>
       </c>
       <c r="B159" t="n">
-        <v>78480</v>
+        <v>78506</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16775,25 +16757,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16803,10 +16785,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>464976</v>
+        <v>465207</v>
       </c>
       <c r="R159" t="n">
-        <v>6823119</v>
+        <v>6822564</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16865,10 +16847,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>117711845</v>
+        <v>117711439</v>
       </c>
       <c r="B160" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16881,21 +16863,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16905,10 +16887,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>465139</v>
+        <v>465238</v>
       </c>
       <c r="R160" t="n">
-        <v>6822785</v>
+        <v>6822512</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16967,10 +16949,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>117711736</v>
+        <v>117711696</v>
       </c>
       <c r="B161" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -16983,37 +16965,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>465029</v>
+        <v>465187</v>
       </c>
       <c r="R161" t="n">
-        <v>6823165</v>
+        <v>6822623</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17048,18 +17027,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -17078,10 +17051,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>117711909</v>
+        <v>117711565</v>
       </c>
       <c r="B162" t="n">
-        <v>78480</v>
+        <v>79590</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17090,38 +17063,41 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>465054</v>
+        <v>465115</v>
       </c>
       <c r="R162" t="n">
-        <v>6822855</v>
+        <v>6822797</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17156,12 +17132,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -17180,10 +17162,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>117711608</v>
+        <v>117711555</v>
       </c>
       <c r="B163" t="n">
-        <v>78506</v>
+        <v>79590</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17196,34 +17178,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6434</v>
+        <v>6462</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>465207</v>
+        <v>464989</v>
       </c>
       <c r="R163" t="n">
-        <v>6822564</v>
+        <v>6822826</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17258,12 +17243,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -17282,10 +17273,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>117711439</v>
+        <v>117711566</v>
       </c>
       <c r="B164" t="n">
-        <v>79098</v>
+        <v>79590</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17294,38 +17285,41 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>465238</v>
+        <v>465130</v>
       </c>
       <c r="R164" t="n">
-        <v>6822512</v>
+        <v>6822768</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17360,12 +17354,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -17384,10 +17384,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>117711696</v>
+        <v>117711658</v>
       </c>
       <c r="B165" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17400,21 +17400,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17424,10 +17424,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>465187</v>
+        <v>464989</v>
       </c>
       <c r="R165" t="n">
-        <v>6822623</v>
+        <v>6823212</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17486,10 +17486,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>117711658</v>
+        <v>117711397</v>
       </c>
       <c r="B166" t="n">
-        <v>78217</v>
+        <v>78514</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17502,21 +17502,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17526,10 +17526,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>464989</v>
+        <v>465229</v>
       </c>
       <c r="R166" t="n">
-        <v>6823212</v>
+        <v>6822789</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19424,10 +19424,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>117711660</v>
+        <v>117711908</v>
       </c>
       <c r="B185" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19440,21 +19440,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19467,7 +19467,7 @@
         <v>465045</v>
       </c>
       <c r="R185" t="n">
-        <v>6823044</v>
+        <v>6822855</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19526,10 +19526,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>117711458</v>
+        <v>117711894</v>
       </c>
       <c r="B186" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19542,21 +19542,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>465184</v>
+        <v>465032</v>
       </c>
       <c r="R186" t="n">
-        <v>6822626</v>
+        <v>6822993</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19628,10 +19628,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>117711489</v>
+        <v>117711888</v>
       </c>
       <c r="B187" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19644,21 +19644,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19668,10 +19668,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>465056</v>
+        <v>465030</v>
       </c>
       <c r="R187" t="n">
-        <v>6823075</v>
+        <v>6823125</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19730,7 +19730,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>117711908</v>
+        <v>117711879</v>
       </c>
       <c r="B188" t="n">
         <v>78480</v>
@@ -19770,10 +19770,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>465045</v>
+        <v>464980</v>
       </c>
       <c r="R188" t="n">
-        <v>6822855</v>
+        <v>6823196</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19832,7 +19832,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>117711894</v>
+        <v>117711853</v>
       </c>
       <c r="B189" t="n">
         <v>78480</v>
@@ -19872,10 +19872,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>465032</v>
+        <v>465129</v>
       </c>
       <c r="R189" t="n">
-        <v>6822993</v>
+        <v>6822859</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19934,7 +19934,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>117711888</v>
+        <v>117711770</v>
       </c>
       <c r="B190" t="n">
         <v>78480</v>
@@ -19974,10 +19974,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>465030</v>
+        <v>465340</v>
       </c>
       <c r="R190" t="n">
-        <v>6823125</v>
+        <v>6822636</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20036,7 +20036,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>117711879</v>
+        <v>117711893</v>
       </c>
       <c r="B191" t="n">
         <v>78480</v>
@@ -20076,10 +20076,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>464980</v>
+        <v>465052</v>
       </c>
       <c r="R191" t="n">
-        <v>6823196</v>
+        <v>6823002</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20138,7 +20138,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>117711853</v>
+        <v>117711865</v>
       </c>
       <c r="B192" t="n">
         <v>78480</v>
@@ -20178,10 +20178,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>465129</v>
+        <v>464973</v>
       </c>
       <c r="R192" t="n">
-        <v>6822859</v>
+        <v>6823085</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20240,7 +20240,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>117711770</v>
+        <v>117711878</v>
       </c>
       <c r="B193" t="n">
         <v>78480</v>
@@ -20280,10 +20280,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>465340</v>
+        <v>464955</v>
       </c>
       <c r="R193" t="n">
-        <v>6822636</v>
+        <v>6823167</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20342,7 +20342,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>117711893</v>
+        <v>117711886</v>
       </c>
       <c r="B194" t="n">
         <v>78480</v>
@@ -20382,10 +20382,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>465052</v>
+        <v>465028</v>
       </c>
       <c r="R194" t="n">
-        <v>6823002</v>
+        <v>6823123</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20444,10 +20444,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>117711865</v>
+        <v>117711619</v>
       </c>
       <c r="B195" t="n">
-        <v>78480</v>
+        <v>79589</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20456,25 +20456,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20484,10 +20484,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>464973</v>
+        <v>465021</v>
       </c>
       <c r="R195" t="n">
-        <v>6823085</v>
+        <v>6822978</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20546,10 +20546,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>117711878</v>
+        <v>117711562</v>
       </c>
       <c r="B196" t="n">
-        <v>78480</v>
+        <v>79590</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20558,38 +20558,41 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>464955</v>
+        <v>465330</v>
       </c>
       <c r="R196" t="n">
-        <v>6823167</v>
+        <v>6822497</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20624,12 +20627,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -20648,10 +20657,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>117711886</v>
+        <v>117711458</v>
       </c>
       <c r="B197" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20664,21 +20673,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20688,10 +20697,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>465028</v>
+        <v>465184</v>
       </c>
       <c r="R197" t="n">
-        <v>6823123</v>
+        <v>6822626</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20750,10 +20759,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>117711619</v>
+        <v>117711489</v>
       </c>
       <c r="B198" t="n">
-        <v>79589</v>
+        <v>79098</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20762,25 +20771,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20790,10 +20799,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>465021</v>
+        <v>465056</v>
       </c>
       <c r="R198" t="n">
-        <v>6822978</v>
+        <v>6823075</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20852,10 +20861,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>117711562</v>
+        <v>117711660</v>
       </c>
       <c r="B199" t="n">
-        <v>79590</v>
+        <v>78217</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -20864,41 +20873,38 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>465330</v>
+        <v>465045</v>
       </c>
       <c r="R199" t="n">
-        <v>6822497</v>
+        <v>6823044</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20933,18 +20939,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
@@ -20963,10 +20963,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>117711735</v>
+        <v>117711405</v>
       </c>
       <c r="B200" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -20979,37 +20979,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>465135</v>
+        <v>465016</v>
       </c>
       <c r="R200" t="n">
-        <v>6822833</v>
+        <v>6823015</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21044,18 +21041,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD200" t="b">
         <v>0</v>
       </c>
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -21074,10 +21065,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>117711911</v>
+        <v>117711995</v>
       </c>
       <c r="B201" t="n">
-        <v>78480</v>
+        <v>78125</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21090,21 +21081,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21114,10 +21105,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>465059</v>
+        <v>465043</v>
       </c>
       <c r="R201" t="n">
-        <v>6822842</v>
+        <v>6822986</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21176,7 +21167,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>117711890</v>
+        <v>117711918</v>
       </c>
       <c r="B202" t="n">
         <v>78480</v>
@@ -21216,10 +21207,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>465064</v>
+        <v>465083</v>
       </c>
       <c r="R202" t="n">
-        <v>6823106</v>
+        <v>6822781</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21278,7 +21269,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>117711848</v>
+        <v>117711735</v>
       </c>
       <c r="B203" t="n">
         <v>78480</v>
@@ -21312,16 +21303,19 @@
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>465126</v>
+        <v>465135</v>
       </c>
       <c r="R203" t="n">
-        <v>6822829</v>
+        <v>6822833</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21356,12 +21350,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD203" t="b">
         <v>0</v>
       </c>
       <c r="AE203" t="b">
         <v>0</v>
       </c>
+      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
@@ -21380,7 +21380,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>117711872</v>
+        <v>117711911</v>
       </c>
       <c r="B204" t="n">
         <v>78480</v>
@@ -21420,10 +21420,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>464915</v>
+        <v>465059</v>
       </c>
       <c r="R204" t="n">
-        <v>6823136</v>
+        <v>6822842</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21482,7 +21482,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>117711916</v>
+        <v>117711890</v>
       </c>
       <c r="B205" t="n">
         <v>78480</v>
@@ -21522,10 +21522,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>465096</v>
+        <v>465064</v>
       </c>
       <c r="R205" t="n">
-        <v>6822795</v>
+        <v>6823106</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21584,7 +21584,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>117711861</v>
+        <v>117711848</v>
       </c>
       <c r="B206" t="n">
         <v>78480</v>
@@ -21624,10 +21624,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>465018</v>
+        <v>465126</v>
       </c>
       <c r="R206" t="n">
-        <v>6823007</v>
+        <v>6822829</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21686,10 +21686,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>117711405</v>
+        <v>117711872</v>
       </c>
       <c r="B207" t="n">
-        <v>78514</v>
+        <v>78480</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -21702,21 +21702,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21726,10 +21726,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>465016</v>
+        <v>464915</v>
       </c>
       <c r="R207" t="n">
-        <v>6823015</v>
+        <v>6823136</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21788,10 +21788,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>117711995</v>
+        <v>117711916</v>
       </c>
       <c r="B208" t="n">
-        <v>78125</v>
+        <v>78480</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21804,21 +21804,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21828,10 +21828,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>465043</v>
+        <v>465096</v>
       </c>
       <c r="R208" t="n">
-        <v>6822986</v>
+        <v>6822795</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21890,7 +21890,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>117711918</v>
+        <v>117711861</v>
       </c>
       <c r="B209" t="n">
         <v>78480</v>
@@ -21930,10 +21930,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>465083</v>
+        <v>465018</v>
       </c>
       <c r="R209" t="n">
-        <v>6822781</v>
+        <v>6823007</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>

--- a/artfynd/A 47952-2023 artfynd.xlsx
+++ b/artfynd/A 47952-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117711891</v>
+        <v>117711394</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465027</v>
+        <v>465395</v>
       </c>
       <c r="R2" t="n">
-        <v>6823022</v>
+        <v>6822489</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117711698</v>
+        <v>117711888</v>
       </c>
       <c r="B3" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465299</v>
+        <v>465030</v>
       </c>
       <c r="R3" t="n">
-        <v>6822674</v>
+        <v>6823125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117711789</v>
+        <v>117711788</v>
       </c>
       <c r="B4" t="n">
         <v>78480</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465120</v>
+        <v>465095</v>
       </c>
       <c r="R4" t="n">
-        <v>6823039</v>
+        <v>6823035</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117711866</v>
+        <v>117711792</v>
       </c>
       <c r="B5" t="n">
         <v>78480</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464983</v>
+        <v>465033</v>
       </c>
       <c r="R5" t="n">
-        <v>6823097</v>
+        <v>6823207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117711869</v>
+        <v>117711928</v>
       </c>
       <c r="B6" t="n">
         <v>78480</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464963</v>
+        <v>464986</v>
       </c>
       <c r="R6" t="n">
-        <v>6823132</v>
+        <v>6822795</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117711473</v>
+        <v>117711474</v>
       </c>
       <c r="B7" t="n">
         <v>79098</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465065</v>
+        <v>465026</v>
       </c>
       <c r="R7" t="n">
-        <v>6822969</v>
+        <v>6823006</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117711656</v>
+        <v>117711478</v>
       </c>
       <c r="B8" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465183</v>
+        <v>464943</v>
       </c>
       <c r="R8" t="n">
-        <v>6822626</v>
+        <v>6823108</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117711651</v>
+        <v>117711440</v>
       </c>
       <c r="B9" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465187</v>
+        <v>465352</v>
       </c>
       <c r="R9" t="n">
-        <v>6822613</v>
+        <v>6822592</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117711523</v>
+        <v>117711886</v>
       </c>
       <c r="B10" t="n">
-        <v>79069</v>
+        <v>78480</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465056</v>
+        <v>465028</v>
       </c>
       <c r="R10" t="n">
-        <v>6823105</v>
+        <v>6823123</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117711657</v>
+        <v>117711890</v>
       </c>
       <c r="B11" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465059</v>
+        <v>465064</v>
       </c>
       <c r="R11" t="n">
-        <v>6822705</v>
+        <v>6823106</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117711732</v>
+        <v>117712005</v>
       </c>
       <c r="B12" t="n">
-        <v>79606</v>
+        <v>91772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229504</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465042</v>
+        <v>465040</v>
       </c>
       <c r="R12" t="n">
-        <v>6822859</v>
+        <v>6822725</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117711408</v>
+        <v>117711768</v>
       </c>
       <c r="B13" t="n">
-        <v>78514</v>
+        <v>78480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465002</v>
+        <v>465394</v>
       </c>
       <c r="R13" t="n">
-        <v>6823046</v>
+        <v>6822493</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117711475</v>
+        <v>117711731</v>
       </c>
       <c r="B14" t="n">
-        <v>79098</v>
+        <v>90648</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465003</v>
+        <v>465012</v>
       </c>
       <c r="R14" t="n">
-        <v>6823040</v>
+        <v>6823041</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117711771</v>
+        <v>117711566</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>79590</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,38 +2013,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465314</v>
+        <v>465130</v>
       </c>
       <c r="R15" t="n">
-        <v>6822659</v>
+        <v>6822768</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,12 +2082,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2103,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117711772</v>
+        <v>117711712</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465258</v>
+        <v>465057</v>
       </c>
       <c r="R16" t="n">
-        <v>6822696</v>
+        <v>6823105</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117711925</v>
+        <v>117711732</v>
       </c>
       <c r="B17" t="n">
-        <v>78480</v>
+        <v>79606</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>229504</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465019</v>
+        <v>465042</v>
       </c>
       <c r="R17" t="n">
-        <v>6822782</v>
+        <v>6822859</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117711919</v>
+        <v>117711660</v>
       </c>
       <c r="B18" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465081</v>
+        <v>465045</v>
       </c>
       <c r="R18" t="n">
-        <v>6822777</v>
+        <v>6823044</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117711611</v>
+        <v>117711584</v>
       </c>
       <c r="B19" t="n">
-        <v>78506</v>
+        <v>79562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2430,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6434</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465028</v>
+        <v>464971</v>
       </c>
       <c r="R19" t="n">
-        <v>6823122</v>
+        <v>6823086</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117711867</v>
+        <v>117711993</v>
       </c>
       <c r="B20" t="n">
-        <v>78480</v>
+        <v>78125</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464978</v>
+        <v>465056</v>
       </c>
       <c r="R20" t="n">
-        <v>6823101</v>
+        <v>6823075</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117711710</v>
+        <v>117711823</v>
       </c>
       <c r="B21" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2638,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465058</v>
+        <v>465157</v>
       </c>
       <c r="R21" t="n">
-        <v>6822707</v>
+        <v>6822719</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2724,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117711884</v>
+        <v>117711735</v>
       </c>
       <c r="B22" t="n">
         <v>78480</v>
@@ -2749,16 +2758,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465002</v>
+        <v>465135</v>
       </c>
       <c r="R22" t="n">
-        <v>6823138</v>
+        <v>6822833</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2793,12 +2805,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2817,7 +2835,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117711820</v>
+        <v>117711904</v>
       </c>
       <c r="B23" t="n">
         <v>78480</v>
@@ -2857,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465186</v>
+        <v>465051</v>
       </c>
       <c r="R23" t="n">
-        <v>6822793</v>
+        <v>6822914</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2937,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117711468</v>
+        <v>117711881</v>
       </c>
       <c r="B24" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2953,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465151</v>
+        <v>465010</v>
       </c>
       <c r="R24" t="n">
-        <v>6822788</v>
+        <v>6823186</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3039,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117711827</v>
+        <v>117711483</v>
       </c>
       <c r="B25" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3055,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465273</v>
+        <v>464993</v>
       </c>
       <c r="R25" t="n">
-        <v>6822555</v>
+        <v>6823209</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3141,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117711843</v>
+        <v>117711711</v>
       </c>
       <c r="B26" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3157,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3181,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465110</v>
+        <v>465071</v>
       </c>
       <c r="R26" t="n">
-        <v>6822717</v>
+        <v>6822963</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,7 +3243,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117711493</v>
+        <v>117711468</v>
       </c>
       <c r="B27" t="n">
         <v>79098</v>
@@ -3265,10 +3283,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465091</v>
+        <v>465151</v>
       </c>
       <c r="R27" t="n">
-        <v>6822828</v>
+        <v>6822788</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3345,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117711492</v>
+        <v>117711853</v>
       </c>
       <c r="B28" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3361,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3385,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465025</v>
+        <v>465129</v>
       </c>
       <c r="R28" t="n">
-        <v>6822860</v>
+        <v>6822859</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3447,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117711483</v>
+        <v>117711861</v>
       </c>
       <c r="B29" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3463,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3487,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464993</v>
+        <v>465018</v>
       </c>
       <c r="R29" t="n">
-        <v>6823209</v>
+        <v>6823007</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3549,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117711482</v>
+        <v>117711773</v>
       </c>
       <c r="B30" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3565,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464989</v>
+        <v>465256</v>
       </c>
       <c r="R30" t="n">
-        <v>6823223</v>
+        <v>6822710</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117711675</v>
+        <v>117711899</v>
       </c>
       <c r="B31" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3667,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465115</v>
+        <v>465008</v>
       </c>
       <c r="R31" t="n">
-        <v>6822797</v>
+        <v>6822955</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3753,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117711404</v>
+        <v>117711492</v>
       </c>
       <c r="B32" t="n">
-        <v>78514</v>
+        <v>79098</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3769,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3793,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465098</v>
+        <v>465025</v>
       </c>
       <c r="R32" t="n">
-        <v>6822909</v>
+        <v>6822860</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3855,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117711831</v>
+        <v>117711476</v>
       </c>
       <c r="B33" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3871,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3895,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465280</v>
+        <v>465003</v>
       </c>
       <c r="R33" t="n">
-        <v>6822526</v>
+        <v>6823046</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3957,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117711830</v>
+        <v>117711995</v>
       </c>
       <c r="B34" t="n">
-        <v>78480</v>
+        <v>78125</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3973,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3997,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465282</v>
+        <v>465043</v>
       </c>
       <c r="R34" t="n">
-        <v>6822525</v>
+        <v>6822986</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,7 +4059,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117711785</v>
+        <v>117711827</v>
       </c>
       <c r="B35" t="n">
         <v>78480</v>
@@ -4081,10 +4099,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465096</v>
+        <v>465273</v>
       </c>
       <c r="R35" t="n">
-        <v>6823017</v>
+        <v>6822555</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,7 +4161,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117711907</v>
+        <v>117711831</v>
       </c>
       <c r="B36" t="n">
         <v>78480</v>
@@ -4183,10 +4201,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465022</v>
+        <v>465280</v>
       </c>
       <c r="R36" t="n">
-        <v>6822851</v>
+        <v>6822526</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4263,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117711653</v>
+        <v>117711761</v>
       </c>
       <c r="B37" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4261,21 +4279,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4303,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465082</v>
+        <v>465039</v>
       </c>
       <c r="R37" t="n">
-        <v>6823073</v>
+        <v>6822657</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4365,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117711991</v>
+        <v>117711771</v>
       </c>
       <c r="B38" t="n">
-        <v>78125</v>
+        <v>78480</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4381,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4405,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465046</v>
+        <v>465314</v>
       </c>
       <c r="R38" t="n">
-        <v>6823084</v>
+        <v>6822659</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4467,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117711775</v>
+        <v>117711562</v>
       </c>
       <c r="B39" t="n">
-        <v>78480</v>
+        <v>79590</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4461,38 +4479,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465240</v>
+        <v>465330</v>
       </c>
       <c r="R39" t="n">
-        <v>6822759</v>
+        <v>6822497</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4527,12 +4548,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4551,10 +4578,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117711479</v>
+        <v>117711611</v>
       </c>
       <c r="B40" t="n">
-        <v>79098</v>
+        <v>78506</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4563,25 +4590,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4618,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464928</v>
+        <v>465028</v>
       </c>
       <c r="R40" t="n">
-        <v>6823159</v>
+        <v>6823122</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4680,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117711697</v>
+        <v>117711555</v>
       </c>
       <c r="B41" t="n">
-        <v>78216</v>
+        <v>79590</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4665,38 +4692,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465233</v>
+        <v>464989</v>
       </c>
       <c r="R41" t="n">
-        <v>6822515</v>
+        <v>6822826</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4731,12 +4761,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4755,10 +4791,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117711470</v>
+        <v>117711909</v>
       </c>
       <c r="B42" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4807,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4831,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465099</v>
+        <v>465054</v>
       </c>
       <c r="R42" t="n">
-        <v>6822897</v>
+        <v>6822855</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,10 +4893,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117711610</v>
+        <v>117711480</v>
       </c>
       <c r="B43" t="n">
-        <v>78506</v>
+        <v>79098</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4869,25 +4905,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4933,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465212</v>
+        <v>464969</v>
       </c>
       <c r="R43" t="n">
-        <v>6822555</v>
+        <v>6823166</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,10 +4995,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117711833</v>
+        <v>117711525</v>
       </c>
       <c r="B44" t="n">
-        <v>78480</v>
+        <v>79069</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4975,21 +5011,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +5035,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465310</v>
+        <v>465045</v>
       </c>
       <c r="R44" t="n">
-        <v>6822472</v>
+        <v>6823044</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,10 +5097,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117711792</v>
+        <v>117711587</v>
       </c>
       <c r="B45" t="n">
-        <v>78480</v>
+        <v>79562</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,21 +5113,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +5137,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465033</v>
+        <v>465115</v>
       </c>
       <c r="R45" t="n">
-        <v>6823207</v>
+        <v>6822796</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,7 +5199,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117711927</v>
+        <v>117711905</v>
       </c>
       <c r="B46" t="n">
         <v>78480</v>
@@ -5203,10 +5239,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464979</v>
+        <v>465056</v>
       </c>
       <c r="R46" t="n">
-        <v>6822792</v>
+        <v>6822904</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5265,7 +5301,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117711923</v>
+        <v>117711778</v>
       </c>
       <c r="B47" t="n">
         <v>78480</v>
@@ -5305,10 +5341,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465060</v>
+        <v>465229</v>
       </c>
       <c r="R47" t="n">
-        <v>6822763</v>
+        <v>6822789</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,7 +5403,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117711856</v>
+        <v>117711777</v>
       </c>
       <c r="B48" t="n">
         <v>78480</v>
@@ -5407,10 +5443,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465118</v>
+        <v>465234</v>
       </c>
       <c r="R48" t="n">
-        <v>6822876</v>
+        <v>6822786</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5505,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117711883</v>
+        <v>117711609</v>
       </c>
       <c r="B49" t="n">
-        <v>78480</v>
+        <v>78506</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5481,25 +5517,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5545,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465030</v>
+        <v>465379</v>
       </c>
       <c r="R49" t="n">
-        <v>6823162</v>
+        <v>6822539</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,7 +5607,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117711478</v>
+        <v>117711491</v>
       </c>
       <c r="B50" t="n">
         <v>79098</v>
@@ -5611,10 +5647,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464943</v>
+        <v>465043</v>
       </c>
       <c r="R50" t="n">
-        <v>6823108</v>
+        <v>6823043</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,10 +5709,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117711652</v>
+        <v>117711675</v>
       </c>
       <c r="B51" t="n">
-        <v>78217</v>
+        <v>79561</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5689,21 +5725,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5713,10 +5749,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465407</v>
+        <v>465115</v>
       </c>
       <c r="R51" t="n">
-        <v>6822454</v>
+        <v>6822797</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5811,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117711625</v>
+        <v>117711416</v>
       </c>
       <c r="B52" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5791,21 +5827,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5815,10 +5851,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465407</v>
+        <v>465431</v>
       </c>
       <c r="R52" t="n">
-        <v>6822451</v>
+        <v>6822517</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5877,7 +5913,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117711858</v>
+        <v>117711862</v>
       </c>
       <c r="B53" t="n">
         <v>78480</v>
@@ -5917,10 +5953,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465091</v>
+        <v>464996</v>
       </c>
       <c r="R53" t="n">
-        <v>6822883</v>
+        <v>6823076</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5979,10 +6015,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117711708</v>
+        <v>117711779</v>
       </c>
       <c r="B54" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5995,21 +6031,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6019,10 +6055,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465185</v>
+        <v>465222</v>
       </c>
       <c r="R54" t="n">
-        <v>6822623</v>
+        <v>6822812</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6081,10 +6117,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117711876</v>
+        <v>117711699</v>
       </c>
       <c r="B55" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6097,21 +6133,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6121,10 +6157,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464928</v>
+        <v>465258</v>
       </c>
       <c r="R55" t="n">
-        <v>6823159</v>
+        <v>6822743</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6183,7 +6219,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117711477</v>
+        <v>117711484</v>
       </c>
       <c r="B56" t="n">
         <v>79098</v>
@@ -6223,10 +6259,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464973</v>
+        <v>465012</v>
       </c>
       <c r="R56" t="n">
-        <v>6823110</v>
+        <v>6823194</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6285,10 +6321,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117711917</v>
+        <v>117711730</v>
       </c>
       <c r="B57" t="n">
-        <v>78480</v>
+        <v>90648</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6297,25 +6333,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6325,10 +6361,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465092</v>
+        <v>465146</v>
       </c>
       <c r="R57" t="n">
-        <v>6822793</v>
+        <v>6822800</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6387,10 +6423,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117711699</v>
+        <v>117711729</v>
       </c>
       <c r="B58" t="n">
-        <v>78216</v>
+        <v>90648</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6399,25 +6435,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6427,10 +6463,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465258</v>
+        <v>465321</v>
       </c>
       <c r="R58" t="n">
-        <v>6822743</v>
+        <v>6822500</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6489,10 +6525,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117711716</v>
+        <v>117711619</v>
       </c>
       <c r="B59" t="n">
-        <v>78216</v>
+        <v>79589</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6501,25 +6537,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6529,10 +6565,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465050</v>
+        <v>465021</v>
       </c>
       <c r="R59" t="n">
-        <v>6822991</v>
+        <v>6822978</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6591,7 +6627,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117711494</v>
+        <v>117711487</v>
       </c>
       <c r="B60" t="n">
         <v>79098</v>
@@ -6631,10 +6667,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465042</v>
+        <v>465063</v>
       </c>
       <c r="R60" t="n">
-        <v>6822770</v>
+        <v>6823088</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6693,10 +6729,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117712003</v>
+        <v>117711494</v>
       </c>
       <c r="B61" t="n">
-        <v>91772</v>
+        <v>79098</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6705,25 +6741,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6769,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465272</v>
+        <v>465042</v>
       </c>
       <c r="R61" t="n">
-        <v>6822559</v>
+        <v>6822770</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6795,10 +6831,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117711584</v>
+        <v>117711408</v>
       </c>
       <c r="B62" t="n">
-        <v>79562</v>
+        <v>78514</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6811,21 +6847,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6835,10 +6871,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464971</v>
+        <v>465002</v>
       </c>
       <c r="R62" t="n">
-        <v>6823086</v>
+        <v>6823046</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6897,10 +6933,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117711730</v>
+        <v>117711897</v>
       </c>
       <c r="B63" t="n">
-        <v>90648</v>
+        <v>78480</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6909,25 +6945,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6937,10 +6973,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465146</v>
+        <v>465002</v>
       </c>
       <c r="R63" t="n">
-        <v>6822800</v>
+        <v>6822972</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6999,10 +7035,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117711734</v>
+        <v>117711903</v>
       </c>
       <c r="B64" t="n">
-        <v>90517</v>
+        <v>78480</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7015,37 +7051,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465126</v>
+        <v>465035</v>
       </c>
       <c r="R64" t="n">
-        <v>6822834</v>
+        <v>6822922</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7080,18 +7113,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Mitt i planerad körväg</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7110,10 +7137,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117711729</v>
+        <v>117711843</v>
       </c>
       <c r="B65" t="n">
-        <v>90648</v>
+        <v>78480</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7122,25 +7149,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7150,10 +7177,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465321</v>
+        <v>465110</v>
       </c>
       <c r="R65" t="n">
-        <v>6822500</v>
+        <v>6822717</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7212,10 +7239,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117711821</v>
+        <v>117711734</v>
       </c>
       <c r="B66" t="n">
-        <v>78480</v>
+        <v>90517</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7228,34 +7255,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465185</v>
+        <v>465126</v>
       </c>
       <c r="R66" t="n">
-        <v>6822757</v>
+        <v>6822834</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7290,12 +7320,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Mitt i planerad körväg</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7314,10 +7350,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117711459</v>
+        <v>117711764</v>
       </c>
       <c r="B67" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7330,21 +7366,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7354,10 +7390,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465193</v>
+        <v>465109</v>
       </c>
       <c r="R67" t="n">
-        <v>6822569</v>
+        <v>6822696</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7416,10 +7452,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117711700</v>
+        <v>117711930</v>
       </c>
       <c r="B68" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7432,21 +7468,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7456,10 +7492,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465104</v>
+        <v>464991</v>
       </c>
       <c r="R68" t="n">
-        <v>6823045</v>
+        <v>6822809</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,10 +7554,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117711394</v>
+        <v>117711651</v>
       </c>
       <c r="B69" t="n">
-        <v>78514</v>
+        <v>78217</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7534,21 +7570,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7558,10 +7594,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465395</v>
+        <v>465187</v>
       </c>
       <c r="R69" t="n">
-        <v>6822489</v>
+        <v>6822613</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7620,10 +7656,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117711491</v>
+        <v>117711656</v>
       </c>
       <c r="B70" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7636,21 +7672,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7660,10 +7696,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465043</v>
+        <v>465183</v>
       </c>
       <c r="R70" t="n">
-        <v>6823043</v>
+        <v>6822626</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7722,10 +7758,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117711543</v>
+        <v>117711991</v>
       </c>
       <c r="B71" t="n">
-        <v>56499</v>
+        <v>78125</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7734,50 +7770,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465107</v>
+        <v>465046</v>
       </c>
       <c r="R71" t="n">
-        <v>6822869</v>
+        <v>6823084</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7836,10 +7860,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117711994</v>
+        <v>117711894</v>
       </c>
       <c r="B72" t="n">
-        <v>78125</v>
+        <v>78480</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7852,21 +7876,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7876,10 +7900,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465054</v>
+        <v>465032</v>
       </c>
       <c r="R72" t="n">
-        <v>6823006</v>
+        <v>6822993</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7938,10 +7962,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117711406</v>
+        <v>117711889</v>
       </c>
       <c r="B73" t="n">
-        <v>78514</v>
+        <v>78480</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7954,21 +7978,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7978,10 +8002,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465008</v>
+        <v>465072</v>
       </c>
       <c r="R73" t="n">
-        <v>6823044</v>
+        <v>6823099</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8040,7 +8064,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117711763</v>
+        <v>117711739</v>
       </c>
       <c r="B74" t="n">
         <v>78480</v>
@@ -8080,10 +8104,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465048</v>
+        <v>465429</v>
       </c>
       <c r="R74" t="n">
-        <v>6822660</v>
+        <v>6822519</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8142,10 +8166,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117711586</v>
+        <v>117711876</v>
       </c>
       <c r="B75" t="n">
-        <v>79562</v>
+        <v>78480</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8158,21 +8182,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8182,10 +8206,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465034</v>
+        <v>464928</v>
       </c>
       <c r="R75" t="n">
-        <v>6822859</v>
+        <v>6823159</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8244,10 +8268,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117711672</v>
+        <v>117711922</v>
       </c>
       <c r="B76" t="n">
-        <v>96797</v>
+        <v>78480</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8256,25 +8280,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8284,10 +8308,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464987</v>
+        <v>465084</v>
       </c>
       <c r="R76" t="n">
-        <v>6823079</v>
+        <v>6822769</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8346,10 +8370,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117711440</v>
+        <v>117711765</v>
       </c>
       <c r="B77" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8362,21 +8386,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8386,10 +8410,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465352</v>
+        <v>465105</v>
       </c>
       <c r="R77" t="n">
-        <v>6822592</v>
+        <v>6822680</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8448,10 +8472,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117711472</v>
+        <v>117711824</v>
       </c>
       <c r="B78" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8464,21 +8488,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8488,10 +8512,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>465070</v>
+        <v>465160</v>
       </c>
       <c r="R78" t="n">
-        <v>6822961</v>
+        <v>6822693</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8550,7 +8574,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117711904</v>
+        <v>117711868</v>
       </c>
       <c r="B79" t="n">
         <v>78480</v>
@@ -8590,10 +8614,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465051</v>
+        <v>464976</v>
       </c>
       <c r="R79" t="n">
-        <v>6822914</v>
+        <v>6823119</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8652,7 +8676,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117711898</v>
+        <v>117711879</v>
       </c>
       <c r="B80" t="n">
         <v>78480</v>
@@ -8692,10 +8716,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465000</v>
+        <v>464980</v>
       </c>
       <c r="R80" t="n">
-        <v>6822960</v>
+        <v>6823196</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8754,7 +8778,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117711912</v>
+        <v>117711825</v>
       </c>
       <c r="B81" t="n">
         <v>78480</v>
@@ -8794,10 +8818,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465072</v>
+        <v>465178</v>
       </c>
       <c r="R81" t="n">
-        <v>6822834</v>
+        <v>6822682</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8856,10 +8880,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117711786</v>
+        <v>117711713</v>
       </c>
       <c r="B82" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8872,21 +8896,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8896,10 +8920,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>465086</v>
+        <v>465046</v>
       </c>
       <c r="R82" t="n">
-        <v>6823030</v>
+        <v>6823046</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8958,10 +8982,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117711823</v>
+        <v>117711697</v>
       </c>
       <c r="B83" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8974,21 +8998,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8998,10 +9022,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>465157</v>
+        <v>465233</v>
       </c>
       <c r="R83" t="n">
-        <v>6822719</v>
+        <v>6822515</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9060,10 +9084,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117711537</v>
+        <v>117711470</v>
       </c>
       <c r="B84" t="n">
-        <v>57287</v>
+        <v>79098</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9076,42 +9100,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>465167</v>
+        <v>465099</v>
       </c>
       <c r="R84" t="n">
-        <v>6822725</v>
+        <v>6822897</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9170,10 +9186,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117712005</v>
+        <v>117711486</v>
       </c>
       <c r="B85" t="n">
-        <v>91772</v>
+        <v>79098</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9182,25 +9198,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9210,10 +9226,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>465040</v>
+        <v>465056</v>
       </c>
       <c r="R85" t="n">
-        <v>6822725</v>
+        <v>6823106</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9272,7 +9288,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117711487</v>
+        <v>117711438</v>
       </c>
       <c r="B86" t="n">
         <v>79098</v>
@@ -9312,10 +9328,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>465063</v>
+        <v>465187</v>
       </c>
       <c r="R86" t="n">
-        <v>6823088</v>
+        <v>6822623</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9374,7 +9390,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117711486</v>
+        <v>117711458</v>
       </c>
       <c r="B87" t="n">
         <v>79098</v>
@@ -9414,10 +9430,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>465056</v>
+        <v>465184</v>
       </c>
       <c r="R87" t="n">
-        <v>6823106</v>
+        <v>6822626</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9476,10 +9492,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117711484</v>
+        <v>117711869</v>
       </c>
       <c r="B88" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9492,21 +9508,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9516,10 +9532,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>465012</v>
+        <v>464963</v>
       </c>
       <c r="R88" t="n">
-        <v>6823194</v>
+        <v>6823132</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9578,10 +9594,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117711826</v>
+        <v>117711493</v>
       </c>
       <c r="B89" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9594,21 +9610,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9618,10 +9634,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>465192</v>
+        <v>465091</v>
       </c>
       <c r="R89" t="n">
-        <v>6822668</v>
+        <v>6822828</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9680,10 +9696,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117711929</v>
+        <v>117711537</v>
       </c>
       <c r="B90" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9696,34 +9712,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464985</v>
+        <v>465167</v>
       </c>
       <c r="R90" t="n">
-        <v>6822805</v>
+        <v>6822725</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9782,10 +9806,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117711476</v>
+        <v>117711891</v>
       </c>
       <c r="B91" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9798,21 +9822,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9822,10 +9846,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>465003</v>
+        <v>465027</v>
       </c>
       <c r="R91" t="n">
-        <v>6823046</v>
+        <v>6823022</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9884,10 +9908,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117711564</v>
+        <v>117711907</v>
       </c>
       <c r="B92" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9896,41 +9920,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>465043</v>
+        <v>465022</v>
       </c>
       <c r="R92" t="n">
-        <v>6822864</v>
+        <v>6822851</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9965,18 +9986,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9995,10 +10010,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117711383</v>
+        <v>117711858</v>
       </c>
       <c r="B93" t="n">
-        <v>74592</v>
+        <v>78480</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10011,21 +10026,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10035,10 +10050,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>465251</v>
+        <v>465091</v>
       </c>
       <c r="R93" t="n">
-        <v>6822507</v>
+        <v>6822883</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10097,7 +10112,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117711829</v>
+        <v>117711926</v>
       </c>
       <c r="B94" t="n">
         <v>78480</v>
@@ -10137,10 +10152,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>465274</v>
+        <v>464988</v>
       </c>
       <c r="R94" t="n">
-        <v>6822528</v>
+        <v>6822780</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10199,7 +10214,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117711825</v>
+        <v>117711866</v>
       </c>
       <c r="B95" t="n">
         <v>78480</v>
@@ -10239,10 +10254,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>465178</v>
+        <v>464983</v>
       </c>
       <c r="R95" t="n">
-        <v>6822682</v>
+        <v>6823097</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10301,7 +10316,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117711824</v>
+        <v>117711916</v>
       </c>
       <c r="B96" t="n">
         <v>78480</v>
@@ -10341,10 +10356,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>465160</v>
+        <v>465096</v>
       </c>
       <c r="R96" t="n">
-        <v>6822693</v>
+        <v>6822795</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10403,10 +10418,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117711862</v>
+        <v>117711625</v>
       </c>
       <c r="B97" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10419,21 +10434,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10443,10 +10458,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464996</v>
+        <v>465407</v>
       </c>
       <c r="R97" t="n">
-        <v>6823076</v>
+        <v>6822451</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10505,10 +10520,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117711928</v>
+        <v>117711662</v>
       </c>
       <c r="B98" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10521,21 +10536,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10545,10 +10560,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464986</v>
+        <v>465042</v>
       </c>
       <c r="R98" t="n">
-        <v>6822795</v>
+        <v>6822770</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10607,10 +10622,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117711931</v>
+        <v>117711698</v>
       </c>
       <c r="B99" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10623,21 +10638,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10647,10 +10662,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464993</v>
+        <v>465299</v>
       </c>
       <c r="R99" t="n">
-        <v>6822829</v>
+        <v>6822674</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10709,7 +10724,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117711852</v>
+        <v>117711766</v>
       </c>
       <c r="B100" t="n">
         <v>78480</v>
@@ -10749,10 +10764,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465132</v>
+        <v>465122</v>
       </c>
       <c r="R100" t="n">
-        <v>6822856</v>
+        <v>6822673</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10811,7 +10826,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>117711416</v>
+        <v>117711462</v>
       </c>
       <c r="B101" t="n">
         <v>79098</v>
@@ -10851,10 +10866,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>465431</v>
+        <v>465290</v>
       </c>
       <c r="R101" t="n">
-        <v>6822517</v>
+        <v>6822535</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10913,10 +10928,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117711467</v>
+        <v>117711612</v>
       </c>
       <c r="B102" t="n">
-        <v>79098</v>
+        <v>78506</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10925,25 +10940,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10953,10 +10968,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>465057</v>
+        <v>465019</v>
       </c>
       <c r="R102" t="n">
-        <v>6822708</v>
+        <v>6822780</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11015,10 +11030,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117711525</v>
+        <v>117711403</v>
       </c>
       <c r="B103" t="n">
-        <v>79069</v>
+        <v>78514</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11031,21 +11046,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11055,10 +11070,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>465045</v>
+        <v>465258</v>
       </c>
       <c r="R103" t="n">
-        <v>6823044</v>
+        <v>6822486</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11117,7 +11132,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>117711851</v>
+        <v>117711846</v>
       </c>
       <c r="B104" t="n">
         <v>78480</v>
@@ -11157,10 +11172,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>465136</v>
+        <v>465149</v>
       </c>
       <c r="R104" t="n">
-        <v>6822847</v>
+        <v>6822795</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11219,7 +11234,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>117711915</v>
+        <v>117711852</v>
       </c>
       <c r="B105" t="n">
         <v>78480</v>
@@ -11259,10 +11274,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>465102</v>
+        <v>465132</v>
       </c>
       <c r="R105" t="n">
-        <v>6822788</v>
+        <v>6822856</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11321,7 +11336,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>117711926</v>
+        <v>117711822</v>
       </c>
       <c r="B106" t="n">
         <v>78480</v>
@@ -11361,10 +11376,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464988</v>
+        <v>465170</v>
       </c>
       <c r="R106" t="n">
-        <v>6822780</v>
+        <v>6822724</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11423,7 +11438,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>117711778</v>
+        <v>117711829</v>
       </c>
       <c r="B107" t="n">
         <v>78480</v>
@@ -11463,10 +11478,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>465229</v>
+        <v>465274</v>
       </c>
       <c r="R107" t="n">
-        <v>6822789</v>
+        <v>6822528</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11525,7 +11540,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>117711768</v>
+        <v>117711736</v>
       </c>
       <c r="B108" t="n">
         <v>78480</v>
@@ -11559,16 +11574,19 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>465394</v>
+        <v>465029</v>
       </c>
       <c r="R108" t="n">
-        <v>6822493</v>
+        <v>6823165</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11603,12 +11621,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11627,7 +11651,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>117711738</v>
+        <v>117711912</v>
       </c>
       <c r="B109" t="n">
         <v>78480</v>
@@ -11667,10 +11691,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>465426</v>
+        <v>465072</v>
       </c>
       <c r="R109" t="n">
-        <v>6822469</v>
+        <v>6822834</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11729,7 +11753,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>117711913</v>
+        <v>117711769</v>
       </c>
       <c r="B110" t="n">
         <v>78480</v>
@@ -11769,10 +11793,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>465106</v>
+        <v>465379</v>
       </c>
       <c r="R110" t="n">
-        <v>6822818</v>
+        <v>6822539</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11831,7 +11855,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>117711846</v>
+        <v>117711867</v>
       </c>
       <c r="B111" t="n">
         <v>78480</v>
@@ -11871,10 +11895,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>465149</v>
+        <v>464978</v>
       </c>
       <c r="R111" t="n">
-        <v>6822795</v>
+        <v>6823101</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11933,10 +11957,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>117711713</v>
+        <v>117711919</v>
       </c>
       <c r="B112" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11949,21 +11973,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11973,10 +11997,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465046</v>
+        <v>465081</v>
       </c>
       <c r="R112" t="n">
-        <v>6823046</v>
+        <v>6822777</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12035,10 +12059,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>117711461</v>
+        <v>117711880</v>
       </c>
       <c r="B113" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12051,21 +12075,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12075,10 +12099,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>465276</v>
+        <v>465011</v>
       </c>
       <c r="R113" t="n">
-        <v>6822556</v>
+        <v>6823194</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12137,10 +12161,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>117711900</v>
+        <v>117711473</v>
       </c>
       <c r="B114" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12153,21 +12177,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12177,10 +12201,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>465014</v>
+        <v>465065</v>
       </c>
       <c r="R114" t="n">
-        <v>6822962</v>
+        <v>6822969</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12239,10 +12263,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>117711474</v>
+        <v>117711847</v>
       </c>
       <c r="B115" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12255,21 +12279,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12279,10 +12303,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>465026</v>
+        <v>465136</v>
       </c>
       <c r="R115" t="n">
-        <v>6823006</v>
+        <v>6822815</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12341,10 +12365,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>117711773</v>
+        <v>117711672</v>
       </c>
       <c r="B116" t="n">
-        <v>78480</v>
+        <v>96797</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12353,25 +12377,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12381,10 +12405,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>465256</v>
+        <v>464987</v>
       </c>
       <c r="R116" t="n">
-        <v>6822710</v>
+        <v>6823079</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12443,7 +12467,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>117711906</v>
+        <v>117711875</v>
       </c>
       <c r="B117" t="n">
         <v>78480</v>
@@ -12483,10 +12507,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>465048</v>
+        <v>464916</v>
       </c>
       <c r="R117" t="n">
-        <v>6822878</v>
+        <v>6823144</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12545,7 +12569,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>117711924</v>
+        <v>117711834</v>
       </c>
       <c r="B118" t="n">
         <v>78480</v>
@@ -12585,10 +12609,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>465032</v>
+        <v>465301</v>
       </c>
       <c r="R118" t="n">
-        <v>6822777</v>
+        <v>6822474</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12647,7 +12671,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>117711764</v>
+        <v>117711920</v>
       </c>
       <c r="B119" t="n">
         <v>78480</v>
@@ -12687,10 +12711,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>465109</v>
+        <v>465088</v>
       </c>
       <c r="R119" t="n">
-        <v>6822696</v>
+        <v>6822770</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12749,10 +12773,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>117711712</v>
+        <v>117711925</v>
       </c>
       <c r="B120" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12765,21 +12789,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12789,10 +12813,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465057</v>
+        <v>465019</v>
       </c>
       <c r="R120" t="n">
-        <v>6823105</v>
+        <v>6822782</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12851,10 +12875,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>117711993</v>
+        <v>117711717</v>
       </c>
       <c r="B121" t="n">
-        <v>78125</v>
+        <v>78216</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12867,21 +12891,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12894,7 +12918,7 @@
         <v>465056</v>
       </c>
       <c r="R121" t="n">
-        <v>6823075</v>
+        <v>6822933</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12953,10 +12977,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>117711403</v>
+        <v>117711482</v>
       </c>
       <c r="B122" t="n">
-        <v>78514</v>
+        <v>79098</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12969,21 +12993,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12993,10 +13017,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>465258</v>
+        <v>464989</v>
       </c>
       <c r="R122" t="n">
-        <v>6822486</v>
+        <v>6823223</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13055,10 +13079,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>117711914</v>
+        <v>117711472</v>
       </c>
       <c r="B123" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13071,21 +13095,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13095,10 +13119,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>465107</v>
+        <v>465070</v>
       </c>
       <c r="R123" t="n">
-        <v>6822816</v>
+        <v>6822961</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13157,10 +13181,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>117711899</v>
+        <v>117711661</v>
       </c>
       <c r="B124" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13173,21 +13197,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13197,10 +13221,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>465008</v>
+        <v>465051</v>
       </c>
       <c r="R124" t="n">
-        <v>6822955</v>
+        <v>6822925</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13259,7 +13283,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>117711889</v>
+        <v>117711785</v>
       </c>
       <c r="B125" t="n">
         <v>78480</v>
@@ -13299,10 +13323,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>465072</v>
+        <v>465096</v>
       </c>
       <c r="R125" t="n">
-        <v>6823099</v>
+        <v>6823017</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13361,7 +13385,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>117711897</v>
+        <v>117711883</v>
       </c>
       <c r="B126" t="n">
         <v>78480</v>
@@ -13401,10 +13425,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>465002</v>
+        <v>465030</v>
       </c>
       <c r="R126" t="n">
-        <v>6822972</v>
+        <v>6823162</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13463,7 +13487,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>117711880</v>
+        <v>117711929</v>
       </c>
       <c r="B127" t="n">
         <v>78480</v>
@@ -13503,10 +13527,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>465011</v>
+        <v>464985</v>
       </c>
       <c r="R127" t="n">
-        <v>6823194</v>
+        <v>6822805</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13565,7 +13589,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>117711875</v>
+        <v>117711918</v>
       </c>
       <c r="B128" t="n">
         <v>78480</v>
@@ -13605,10 +13629,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>464916</v>
+        <v>465083</v>
       </c>
       <c r="R128" t="n">
-        <v>6823144</v>
+        <v>6822781</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13667,7 +13691,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>117711847</v>
+        <v>117711927</v>
       </c>
       <c r="B129" t="n">
         <v>78480</v>
@@ -13707,10 +13731,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>465136</v>
+        <v>464979</v>
       </c>
       <c r="R129" t="n">
-        <v>6822815</v>
+        <v>6822792</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13769,10 +13793,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>117711903</v>
+        <v>117711475</v>
       </c>
       <c r="B130" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13785,21 +13809,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13809,10 +13833,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>465035</v>
+        <v>465003</v>
       </c>
       <c r="R130" t="n">
-        <v>6822922</v>
+        <v>6823040</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13871,10 +13895,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>117711396</v>
+        <v>117711383</v>
       </c>
       <c r="B131" t="n">
-        <v>78514</v>
+        <v>74592</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13887,21 +13911,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13911,10 +13935,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>465249</v>
+        <v>465251</v>
       </c>
       <c r="R131" t="n">
-        <v>6822748</v>
+        <v>6822507</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13973,10 +13997,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>117711618</v>
+        <v>117711402</v>
       </c>
       <c r="B132" t="n">
-        <v>79589</v>
+        <v>78514</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13985,25 +14009,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6461</v>
+        <v>185</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14013,10 +14037,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>465010</v>
+        <v>465170</v>
       </c>
       <c r="R132" t="n">
-        <v>6823041</v>
+        <v>6822729</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14075,10 +14099,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>117711661</v>
+        <v>117711990</v>
       </c>
       <c r="B133" t="n">
-        <v>78217</v>
+        <v>78125</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14091,21 +14115,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14115,10 +14139,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>465051</v>
+        <v>464988</v>
       </c>
       <c r="R133" t="n">
-        <v>6822925</v>
+        <v>6823222</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14177,10 +14201,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>117711480</v>
+        <v>117711738</v>
       </c>
       <c r="B134" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14193,21 +14217,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14217,10 +14241,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464969</v>
+        <v>465426</v>
       </c>
       <c r="R134" t="n">
-        <v>6823166</v>
+        <v>6822469</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14279,7 +14303,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>117711761</v>
+        <v>117711914</v>
       </c>
       <c r="B135" t="n">
         <v>78480</v>
@@ -14319,10 +14343,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>465039</v>
+        <v>465107</v>
       </c>
       <c r="R135" t="n">
-        <v>6822657</v>
+        <v>6822816</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14381,7 +14405,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>117711881</v>
+        <v>117711842</v>
       </c>
       <c r="B136" t="n">
         <v>78480</v>
@@ -14421,10 +14445,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>465010</v>
+        <v>465106</v>
       </c>
       <c r="R136" t="n">
-        <v>6823186</v>
+        <v>6822702</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14483,7 +14507,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>117711766</v>
+        <v>117711865</v>
       </c>
       <c r="B137" t="n">
         <v>78480</v>
@@ -14523,10 +14547,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>465122</v>
+        <v>464973</v>
       </c>
       <c r="R137" t="n">
-        <v>6822673</v>
+        <v>6823085</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14585,7 +14609,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>117711850</v>
+        <v>117711911</v>
       </c>
       <c r="B138" t="n">
         <v>78480</v>
@@ -14625,7 +14649,7 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>465139</v>
+        <v>465059</v>
       </c>
       <c r="R138" t="n">
         <v>6822842</v>
@@ -14687,7 +14711,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>117711922</v>
+        <v>117711915</v>
       </c>
       <c r="B139" t="n">
         <v>78480</v>
@@ -14727,10 +14751,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>465084</v>
+        <v>465102</v>
       </c>
       <c r="R139" t="n">
-        <v>6822769</v>
+        <v>6822788</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14789,10 +14813,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>117712007</v>
+        <v>117712003</v>
       </c>
       <c r="B140" t="n">
-        <v>79596</v>
+        <v>91772</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14805,21 +14829,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14829,10 +14853,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>465087</v>
+        <v>465272</v>
       </c>
       <c r="R140" t="n">
-        <v>6822688</v>
+        <v>6822559</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14891,10 +14915,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>117711620</v>
+        <v>117711917</v>
       </c>
       <c r="B141" t="n">
-        <v>79589</v>
+        <v>78480</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14903,25 +14927,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14931,10 +14955,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>465060</v>
+        <v>465092</v>
       </c>
       <c r="R141" t="n">
-        <v>6822839</v>
+        <v>6822793</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14993,10 +15017,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>117711563</v>
+        <v>117711708</v>
       </c>
       <c r="B142" t="n">
-        <v>79590</v>
+        <v>78216</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15005,41 +15029,38 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>465121</v>
+        <v>465185</v>
       </c>
       <c r="R142" t="n">
-        <v>6822755</v>
+        <v>6822623</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15074,18 +15095,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15104,10 +15119,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>117711731</v>
+        <v>117711715</v>
       </c>
       <c r="B143" t="n">
-        <v>90648</v>
+        <v>78216</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15116,25 +15131,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15144,10 +15159,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>465012</v>
+        <v>465052</v>
       </c>
       <c r="R143" t="n">
-        <v>6823041</v>
+        <v>6823001</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15206,10 +15221,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>117711485</v>
+        <v>117711923</v>
       </c>
       <c r="B144" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15222,21 +15237,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15246,10 +15261,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>465022</v>
+        <v>465060</v>
       </c>
       <c r="R144" t="n">
-        <v>6823158</v>
+        <v>6822763</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15308,7 +15323,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>117711587</v>
+        <v>117711586</v>
       </c>
       <c r="B145" t="n">
         <v>79562</v>
@@ -15348,10 +15363,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>465115</v>
+        <v>465034</v>
       </c>
       <c r="R145" t="n">
-        <v>6822796</v>
+        <v>6822859</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15410,10 +15425,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>117711765</v>
+        <v>117711477</v>
       </c>
       <c r="B146" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15426,21 +15441,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15450,10 +15465,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>465105</v>
+        <v>464973</v>
       </c>
       <c r="R146" t="n">
-        <v>6822680</v>
+        <v>6823110</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15512,10 +15527,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>117711873</v>
+        <v>117711674</v>
       </c>
       <c r="B147" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15528,21 +15543,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15552,10 +15567,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>464912</v>
+        <v>465071</v>
       </c>
       <c r="R147" t="n">
-        <v>6823140</v>
+        <v>6822839</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15614,10 +15629,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>117711715</v>
+        <v>117711489</v>
       </c>
       <c r="B148" t="n">
-        <v>78216</v>
+        <v>79098</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15630,21 +15645,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15654,10 +15669,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>465052</v>
+        <v>465056</v>
       </c>
       <c r="R148" t="n">
-        <v>6823001</v>
+        <v>6823075</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15716,10 +15731,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>117711930</v>
+        <v>117711716</v>
       </c>
       <c r="B149" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15732,21 +15747,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15756,10 +15771,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464991</v>
+        <v>465050</v>
       </c>
       <c r="R149" t="n">
-        <v>6822809</v>
+        <v>6822991</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15818,10 +15833,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>117711407</v>
+        <v>117711523</v>
       </c>
       <c r="B150" t="n">
-        <v>78514</v>
+        <v>79069</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15834,21 +15849,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15858,10 +15873,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>465007</v>
+        <v>465056</v>
       </c>
       <c r="R150" t="n">
-        <v>6823041</v>
+        <v>6823105</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15920,10 +15935,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>117711842</v>
+        <v>117711657</v>
       </c>
       <c r="B151" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15936,21 +15951,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15960,10 +15975,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>465106</v>
+        <v>465059</v>
       </c>
       <c r="R151" t="n">
-        <v>6822702</v>
+        <v>6822705</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16022,10 +16037,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>117711769</v>
+        <v>117711404</v>
       </c>
       <c r="B152" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16038,21 +16053,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16062,10 +16077,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>465379</v>
+        <v>465098</v>
       </c>
       <c r="R152" t="n">
-        <v>6822539</v>
+        <v>6822909</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16124,10 +16139,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>117711895</v>
+        <v>117711405</v>
       </c>
       <c r="B153" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16140,21 +16155,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16164,10 +16179,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>465019</v>
+        <v>465016</v>
       </c>
       <c r="R153" t="n">
-        <v>6822976</v>
+        <v>6823015</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16226,10 +16241,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>117711788</v>
+        <v>117712007</v>
       </c>
       <c r="B154" t="n">
-        <v>78480</v>
+        <v>79596</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16238,20 +16253,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -16266,10 +16281,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>465095</v>
+        <v>465087</v>
       </c>
       <c r="R154" t="n">
-        <v>6823035</v>
+        <v>6822688</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16328,10 +16343,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>117711868</v>
+        <v>117711658</v>
       </c>
       <c r="B155" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16344,21 +16359,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16368,10 +16383,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>464976</v>
+        <v>464989</v>
       </c>
       <c r="R155" t="n">
-        <v>6823119</v>
+        <v>6823212</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16532,7 +16547,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>117711736</v>
+        <v>117711906</v>
       </c>
       <c r="B157" t="n">
         <v>78480</v>
@@ -16566,19 +16581,16 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>465029</v>
+        <v>465048</v>
       </c>
       <c r="R157" t="n">
-        <v>6823165</v>
+        <v>6822878</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16613,18 +16625,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -16643,7 +16649,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>117711909</v>
+        <v>117711826</v>
       </c>
       <c r="B158" t="n">
         <v>78480</v>
@@ -16683,10 +16689,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>465054</v>
+        <v>465192</v>
       </c>
       <c r="R158" t="n">
-        <v>6822855</v>
+        <v>6822668</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16745,10 +16751,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>117711608</v>
+        <v>117711908</v>
       </c>
       <c r="B159" t="n">
-        <v>78506</v>
+        <v>78480</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16757,25 +16763,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16785,10 +16791,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>465207</v>
+        <v>465045</v>
       </c>
       <c r="R159" t="n">
-        <v>6822564</v>
+        <v>6822855</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16847,10 +16853,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>117711439</v>
+        <v>117711873</v>
       </c>
       <c r="B160" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16863,21 +16869,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16887,10 +16893,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>465238</v>
+        <v>464912</v>
       </c>
       <c r="R160" t="n">
-        <v>6822512</v>
+        <v>6823140</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16949,10 +16955,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>117711696</v>
+        <v>117711407</v>
       </c>
       <c r="B161" t="n">
-        <v>78216</v>
+        <v>78514</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -16965,21 +16971,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16989,10 +16995,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>465187</v>
+        <v>465007</v>
       </c>
       <c r="R161" t="n">
-        <v>6822623</v>
+        <v>6823041</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17051,10 +17057,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>117711565</v>
+        <v>117711786</v>
       </c>
       <c r="B162" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17063,41 +17069,38 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>465115</v>
+        <v>465086</v>
       </c>
       <c r="R162" t="n">
-        <v>6822797</v>
+        <v>6823030</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17132,18 +17135,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -17162,10 +17159,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>117711555</v>
+        <v>117711884</v>
       </c>
       <c r="B163" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17174,41 +17171,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>464989</v>
+        <v>465002</v>
       </c>
       <c r="R163" t="n">
-        <v>6822826</v>
+        <v>6823138</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17243,18 +17237,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>På rönn</t>
-        </is>
-      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -17273,10 +17261,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>117711566</v>
+        <v>117711740</v>
       </c>
       <c r="B164" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17285,41 +17273,38 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>465130</v>
+        <v>465415</v>
       </c>
       <c r="R164" t="n">
-        <v>6822768</v>
+        <v>6822567</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17354,18 +17339,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -17384,10 +17363,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>117711658</v>
+        <v>117711850</v>
       </c>
       <c r="B165" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17400,21 +17379,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17424,10 +17403,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>464989</v>
+        <v>465139</v>
       </c>
       <c r="R165" t="n">
-        <v>6823212</v>
+        <v>6822842</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17486,10 +17465,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>117711397</v>
+        <v>117711900</v>
       </c>
       <c r="B166" t="n">
-        <v>78514</v>
+        <v>78480</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17502,21 +17481,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17526,10 +17505,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>465229</v>
+        <v>465014</v>
       </c>
       <c r="R166" t="n">
-        <v>6822789</v>
+        <v>6822962</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17588,10 +17567,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>117711822</v>
+        <v>117711565</v>
       </c>
       <c r="B167" t="n">
-        <v>78480</v>
+        <v>79590</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17600,38 +17579,41 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>465170</v>
+        <v>465115</v>
       </c>
       <c r="R167" t="n">
-        <v>6822724</v>
+        <v>6822797</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17666,12 +17648,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -17690,10 +17678,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>117711740</v>
+        <v>117711700</v>
       </c>
       <c r="B168" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17706,21 +17694,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17730,10 +17718,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>465415</v>
+        <v>465104</v>
       </c>
       <c r="R168" t="n">
-        <v>6822567</v>
+        <v>6823045</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17792,10 +17780,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>117711739</v>
+        <v>117711467</v>
       </c>
       <c r="B169" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17808,21 +17796,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17832,10 +17820,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>465429</v>
+        <v>465057</v>
       </c>
       <c r="R169" t="n">
-        <v>6822519</v>
+        <v>6822708</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17894,10 +17882,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>117711609</v>
+        <v>117711564</v>
       </c>
       <c r="B170" t="n">
-        <v>78506</v>
+        <v>79590</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17910,34 +17898,37 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6434</v>
+        <v>6462</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>465379</v>
+        <v>465043</v>
       </c>
       <c r="R170" t="n">
-        <v>6822539</v>
+        <v>6822864</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17972,12 +17963,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -17996,10 +17993,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>117711905</v>
+        <v>117711994</v>
       </c>
       <c r="B171" t="n">
-        <v>78480</v>
+        <v>78125</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18012,21 +18009,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18036,10 +18033,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>465056</v>
+        <v>465054</v>
       </c>
       <c r="R171" t="n">
-        <v>6822904</v>
+        <v>6823006</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18098,7 +18095,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>117711834</v>
+        <v>117711763</v>
       </c>
       <c r="B172" t="n">
         <v>78480</v>
@@ -18138,10 +18135,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>465301</v>
+        <v>465048</v>
       </c>
       <c r="R172" t="n">
-        <v>6822474</v>
+        <v>6822660</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18200,10 +18197,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>117711711</v>
+        <v>117711653</v>
       </c>
       <c r="B173" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18216,21 +18213,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18240,10 +18237,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>465071</v>
+        <v>465082</v>
       </c>
       <c r="R173" t="n">
-        <v>6822963</v>
+        <v>6823073</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18302,7 +18299,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>117711920</v>
+        <v>117711789</v>
       </c>
       <c r="B174" t="n">
         <v>78480</v>
@@ -18342,10 +18339,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>465088</v>
+        <v>465120</v>
       </c>
       <c r="R174" t="n">
-        <v>6822770</v>
+        <v>6823039</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18404,10 +18401,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>117711662</v>
+        <v>117711924</v>
       </c>
       <c r="B175" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18420,21 +18417,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18444,10 +18441,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>465042</v>
+        <v>465032</v>
       </c>
       <c r="R175" t="n">
-        <v>6822770</v>
+        <v>6822777</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18506,10 +18503,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>117711990</v>
+        <v>117711775</v>
       </c>
       <c r="B176" t="n">
-        <v>78125</v>
+        <v>78480</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18522,21 +18519,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18546,10 +18543,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>464988</v>
+        <v>465240</v>
       </c>
       <c r="R176" t="n">
-        <v>6823222</v>
+        <v>6822759</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18608,10 +18605,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>117711717</v>
+        <v>117711833</v>
       </c>
       <c r="B177" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18624,21 +18621,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18648,10 +18645,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>465056</v>
+        <v>465310</v>
       </c>
       <c r="R177" t="n">
-        <v>6822933</v>
+        <v>6822472</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18710,7 +18707,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>117711882</v>
+        <v>117711820</v>
       </c>
       <c r="B178" t="n">
         <v>78480</v>
@@ -18750,10 +18747,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>465023</v>
+        <v>465186</v>
       </c>
       <c r="R178" t="n">
-        <v>6823173</v>
+        <v>6822793</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18812,7 +18809,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>117711777</v>
+        <v>117711893</v>
       </c>
       <c r="B179" t="n">
         <v>78480</v>
@@ -18852,10 +18849,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>465234</v>
+        <v>465052</v>
       </c>
       <c r="R179" t="n">
-        <v>6822786</v>
+        <v>6823002</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18914,10 +18911,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>117711779</v>
+        <v>117711710</v>
       </c>
       <c r="B180" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18930,21 +18927,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18954,10 +18951,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>465222</v>
+        <v>465058</v>
       </c>
       <c r="R180" t="n">
-        <v>6822812</v>
+        <v>6822707</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19016,7 +19013,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>117711612</v>
+        <v>117711610</v>
       </c>
       <c r="B181" t="n">
         <v>78506</v>
@@ -19056,10 +19053,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>465019</v>
+        <v>465212</v>
       </c>
       <c r="R181" t="n">
-        <v>6822780</v>
+        <v>6822555</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19118,10 +19115,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>117711674</v>
+        <v>117711459</v>
       </c>
       <c r="B182" t="n">
-        <v>79561</v>
+        <v>79098</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19134,21 +19131,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19158,10 +19155,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>465071</v>
+        <v>465193</v>
       </c>
       <c r="R182" t="n">
-        <v>6822839</v>
+        <v>6822569</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19220,10 +19217,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>117711402</v>
+        <v>117711563</v>
       </c>
       <c r="B183" t="n">
-        <v>78514</v>
+        <v>79590</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19232,38 +19229,41 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>465170</v>
+        <v>465121</v>
       </c>
       <c r="R183" t="n">
-        <v>6822729</v>
+        <v>6822755</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19298,12 +19298,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD183" t="b">
         <v>0</v>
       </c>
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -19322,10 +19328,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>117711659</v>
+        <v>117711851</v>
       </c>
       <c r="B184" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19338,21 +19344,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19362,10 +19368,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>465007</v>
+        <v>465136</v>
       </c>
       <c r="R184" t="n">
-        <v>6823134</v>
+        <v>6822847</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19424,7 +19430,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>117711908</v>
+        <v>117711898</v>
       </c>
       <c r="B185" t="n">
         <v>78480</v>
@@ -19464,10 +19470,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>465045</v>
+        <v>465000</v>
       </c>
       <c r="R185" t="n">
-        <v>6822855</v>
+        <v>6822960</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19526,7 +19532,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>117711894</v>
+        <v>117711772</v>
       </c>
       <c r="B186" t="n">
         <v>78480</v>
@@ -19566,10 +19572,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>465032</v>
+        <v>465258</v>
       </c>
       <c r="R186" t="n">
-        <v>6822993</v>
+        <v>6822696</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19628,7 +19634,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>117711888</v>
+        <v>117711770</v>
       </c>
       <c r="B187" t="n">
         <v>78480</v>
@@ -19668,10 +19674,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>465030</v>
+        <v>465340</v>
       </c>
       <c r="R187" t="n">
-        <v>6823125</v>
+        <v>6822636</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19730,10 +19736,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>117711879</v>
+        <v>117711543</v>
       </c>
       <c r="B188" t="n">
-        <v>78480</v>
+        <v>56499</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19742,38 +19748,50 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>464980</v>
+        <v>465107</v>
       </c>
       <c r="R188" t="n">
-        <v>6823196</v>
+        <v>6822869</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19832,10 +19850,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>117711853</v>
+        <v>117711652</v>
       </c>
       <c r="B189" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19848,21 +19866,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19872,10 +19890,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>465129</v>
+        <v>465407</v>
       </c>
       <c r="R189" t="n">
-        <v>6822859</v>
+        <v>6822454</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19934,10 +19952,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>117711770</v>
+        <v>117711397</v>
       </c>
       <c r="B190" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -19950,21 +19968,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19974,10 +19992,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>465340</v>
+        <v>465229</v>
       </c>
       <c r="R190" t="n">
-        <v>6822636</v>
+        <v>6822789</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20036,10 +20054,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>117711893</v>
+        <v>117711396</v>
       </c>
       <c r="B191" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20052,21 +20070,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20076,10 +20094,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>465052</v>
+        <v>465249</v>
       </c>
       <c r="R191" t="n">
-        <v>6823002</v>
+        <v>6822748</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20138,10 +20156,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>117711865</v>
+        <v>117711479</v>
       </c>
       <c r="B192" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20154,21 +20172,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20178,10 +20196,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>464973</v>
+        <v>464928</v>
       </c>
       <c r="R192" t="n">
-        <v>6823085</v>
+        <v>6823159</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20240,7 +20258,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>117711878</v>
+        <v>117711821</v>
       </c>
       <c r="B193" t="n">
         <v>78480</v>
@@ -20280,10 +20298,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>464955</v>
+        <v>465185</v>
       </c>
       <c r="R193" t="n">
-        <v>6823167</v>
+        <v>6822757</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20342,10 +20360,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>117711886</v>
+        <v>117711620</v>
       </c>
       <c r="B194" t="n">
-        <v>78480</v>
+        <v>79589</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20354,25 +20372,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20382,10 +20400,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>465028</v>
+        <v>465060</v>
       </c>
       <c r="R194" t="n">
-        <v>6823123</v>
+        <v>6822839</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20444,7 +20462,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>117711619</v>
+        <v>117711618</v>
       </c>
       <c r="B195" t="n">
         <v>79589</v>
@@ -20484,10 +20502,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>465021</v>
+        <v>465010</v>
       </c>
       <c r="R195" t="n">
-        <v>6822978</v>
+        <v>6823041</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20546,10 +20564,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>117711562</v>
+        <v>117711439</v>
       </c>
       <c r="B196" t="n">
-        <v>79590</v>
+        <v>79098</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20558,41 +20576,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>465330</v>
+        <v>465238</v>
       </c>
       <c r="R196" t="n">
-        <v>6822497</v>
+        <v>6822512</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20627,18 +20642,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -20657,7 +20666,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>117711458</v>
+        <v>117711485</v>
       </c>
       <c r="B197" t="n">
         <v>79098</v>
@@ -20697,10 +20706,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>465184</v>
+        <v>465022</v>
       </c>
       <c r="R197" t="n">
-        <v>6822626</v>
+        <v>6823158</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20759,10 +20768,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>117711489</v>
+        <v>117711878</v>
       </c>
       <c r="B198" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20775,21 +20784,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20799,10 +20808,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>465056</v>
+        <v>464955</v>
       </c>
       <c r="R198" t="n">
-        <v>6823075</v>
+        <v>6823167</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20861,10 +20870,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>117711660</v>
+        <v>117711931</v>
       </c>
       <c r="B199" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -20877,21 +20886,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20901,10 +20910,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>465045</v>
+        <v>464993</v>
       </c>
       <c r="R199" t="n">
-        <v>6823044</v>
+        <v>6822829</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20963,10 +20972,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>117711405</v>
+        <v>117711856</v>
       </c>
       <c r="B200" t="n">
-        <v>78514</v>
+        <v>78480</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -20979,21 +20988,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21003,10 +21012,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>465016</v>
+        <v>465118</v>
       </c>
       <c r="R200" t="n">
-        <v>6823015</v>
+        <v>6822876</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21065,10 +21074,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>117711995</v>
+        <v>117711830</v>
       </c>
       <c r="B201" t="n">
-        <v>78125</v>
+        <v>78480</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21081,21 +21090,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21105,10 +21114,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>465043</v>
+        <v>465282</v>
       </c>
       <c r="R201" t="n">
-        <v>6822986</v>
+        <v>6822525</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21167,7 +21176,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>117711918</v>
+        <v>117711848</v>
       </c>
       <c r="B202" t="n">
         <v>78480</v>
@@ -21207,10 +21216,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>465083</v>
+        <v>465126</v>
       </c>
       <c r="R202" t="n">
-        <v>6822781</v>
+        <v>6822829</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21269,7 +21278,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>117711735</v>
+        <v>117711882</v>
       </c>
       <c r="B203" t="n">
         <v>78480</v>
@@ -21303,19 +21312,16 @@
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>465135</v>
+        <v>465023</v>
       </c>
       <c r="R203" t="n">
-        <v>6822833</v>
+        <v>6823173</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21350,18 +21356,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD203" t="b">
         <v>0</v>
       </c>
       <c r="AE203" t="b">
         <v>0</v>
       </c>
-      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
@@ -21380,10 +21380,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>117711911</v>
+        <v>117711461</v>
       </c>
       <c r="B204" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21396,21 +21396,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21420,10 +21420,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>465059</v>
+        <v>465276</v>
       </c>
       <c r="R204" t="n">
-        <v>6822842</v>
+        <v>6822556</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21482,10 +21482,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>117711890</v>
+        <v>117711608</v>
       </c>
       <c r="B205" t="n">
-        <v>78480</v>
+        <v>78506</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21494,25 +21494,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21522,10 +21522,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>465064</v>
+        <v>465207</v>
       </c>
       <c r="R205" t="n">
-        <v>6823106</v>
+        <v>6822564</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21584,10 +21584,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>117711848</v>
+        <v>117711406</v>
       </c>
       <c r="B206" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21600,21 +21600,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21624,10 +21624,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>465126</v>
+        <v>465008</v>
       </c>
       <c r="R206" t="n">
-        <v>6822829</v>
+        <v>6823044</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21686,7 +21686,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>117711872</v>
+        <v>117711895</v>
       </c>
       <c r="B207" t="n">
         <v>78480</v>
@@ -21726,10 +21726,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>464915</v>
+        <v>465019</v>
       </c>
       <c r="R207" t="n">
-        <v>6823136</v>
+        <v>6822976</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21788,7 +21788,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>117711916</v>
+        <v>117711872</v>
       </c>
       <c r="B208" t="n">
         <v>78480</v>
@@ -21828,10 +21828,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>465096</v>
+        <v>464915</v>
       </c>
       <c r="R208" t="n">
-        <v>6822795</v>
+        <v>6823136</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21890,7 +21890,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>117711861</v>
+        <v>117711913</v>
       </c>
       <c r="B209" t="n">
         <v>78480</v>
@@ -21930,10 +21930,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>465018</v>
+        <v>465106</v>
       </c>
       <c r="R209" t="n">
-        <v>6823007</v>
+        <v>6822818</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21992,10 +21992,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>117711438</v>
+        <v>117711696</v>
       </c>
       <c r="B210" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22008,21 +22008,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -22094,10 +22094,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>117711462</v>
+        <v>117711659</v>
       </c>
       <c r="B211" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22110,21 +22110,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22134,10 +22134,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>465290</v>
+        <v>465007</v>
       </c>
       <c r="R211" t="n">
-        <v>6822535</v>
+        <v>6823134</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>

--- a/artfynd/A 47952-2023 artfynd.xlsx
+++ b/artfynd/A 47952-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117711394</v>
+        <v>117711715</v>
       </c>
       <c r="B2" t="n">
-        <v>78514</v>
+        <v>78218</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465395</v>
+        <v>465052</v>
       </c>
       <c r="R2" t="n">
-        <v>6822489</v>
+        <v>6823001</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117711888</v>
+        <v>117711656</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465030</v>
+        <v>465183</v>
       </c>
       <c r="R3" t="n">
-        <v>6823125</v>
+        <v>6822626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117711788</v>
+        <v>117711657</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465095</v>
+        <v>465059</v>
       </c>
       <c r="R4" t="n">
-        <v>6823035</v>
+        <v>6822705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117711792</v>
+        <v>117711865</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465033</v>
+        <v>464973</v>
       </c>
       <c r="R5" t="n">
-        <v>6823207</v>
+        <v>6823085</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117711928</v>
+        <v>117711917</v>
       </c>
       <c r="B6" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464986</v>
+        <v>465092</v>
       </c>
       <c r="R6" t="n">
-        <v>6822795</v>
+        <v>6822793</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117711474</v>
+        <v>117711822</v>
       </c>
       <c r="B7" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465026</v>
+        <v>465170</v>
       </c>
       <c r="R7" t="n">
-        <v>6823006</v>
+        <v>6822724</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117711478</v>
+        <v>117711883</v>
       </c>
       <c r="B8" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464943</v>
+        <v>465030</v>
       </c>
       <c r="R8" t="n">
-        <v>6823108</v>
+        <v>6823162</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117711440</v>
+        <v>117711563</v>
       </c>
       <c r="B9" t="n">
-        <v>79098</v>
+        <v>79592</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,38 +1401,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465352</v>
+        <v>465121</v>
       </c>
       <c r="R9" t="n">
-        <v>6822592</v>
+        <v>6822755</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,12 +1470,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117711886</v>
+        <v>117711738</v>
       </c>
       <c r="B10" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465028</v>
+        <v>465426</v>
       </c>
       <c r="R10" t="n">
-        <v>6823123</v>
+        <v>6822469</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117711890</v>
+        <v>117711468</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465064</v>
+        <v>465151</v>
       </c>
       <c r="R11" t="n">
-        <v>6823106</v>
+        <v>6822788</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117712005</v>
+        <v>117711925</v>
       </c>
       <c r="B12" t="n">
-        <v>91772</v>
+        <v>78482</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465040</v>
+        <v>465019</v>
       </c>
       <c r="R12" t="n">
-        <v>6822725</v>
+        <v>6822782</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117711768</v>
+        <v>117711894</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465394</v>
+        <v>465032</v>
       </c>
       <c r="R13" t="n">
-        <v>6822493</v>
+        <v>6822993</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117711731</v>
+        <v>117711493</v>
       </c>
       <c r="B14" t="n">
-        <v>90648</v>
+        <v>79100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465012</v>
+        <v>465091</v>
       </c>
       <c r="R14" t="n">
-        <v>6823041</v>
+        <v>6822828</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117711566</v>
+        <v>117711821</v>
       </c>
       <c r="B15" t="n">
-        <v>79590</v>
+        <v>78482</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,41 +2022,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465130</v>
+        <v>465185</v>
       </c>
       <c r="R15" t="n">
-        <v>6822768</v>
+        <v>6822757</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,18 +2088,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117711712</v>
+        <v>117711923</v>
       </c>
       <c r="B16" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465057</v>
+        <v>465060</v>
       </c>
       <c r="R16" t="n">
-        <v>6823105</v>
+        <v>6822763</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117711732</v>
+        <v>117711659</v>
       </c>
       <c r="B17" t="n">
-        <v>79606</v>
+        <v>78219</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229504</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465042</v>
+        <v>465007</v>
       </c>
       <c r="R17" t="n">
-        <v>6822859</v>
+        <v>6823134</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117711660</v>
+        <v>117711662</v>
       </c>
       <c r="B18" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465045</v>
+        <v>465042</v>
       </c>
       <c r="R18" t="n">
-        <v>6823044</v>
+        <v>6822770</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117711584</v>
+        <v>117711734</v>
       </c>
       <c r="B19" t="n">
-        <v>79562</v>
+        <v>90519</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,34 +2434,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464971</v>
+        <v>465126</v>
       </c>
       <c r="R19" t="n">
-        <v>6823086</v>
+        <v>6822834</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2496,12 +2499,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mitt i planerad körväg</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2520,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117711993</v>
+        <v>117711586</v>
       </c>
       <c r="B20" t="n">
-        <v>78125</v>
+        <v>79564</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2545,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465056</v>
+        <v>465034</v>
       </c>
       <c r="R20" t="n">
-        <v>6823075</v>
+        <v>6822859</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,10 +2631,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117711823</v>
+        <v>117711675</v>
       </c>
       <c r="B21" t="n">
-        <v>78480</v>
+        <v>79563</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2638,21 +2647,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465157</v>
+        <v>465115</v>
       </c>
       <c r="R21" t="n">
-        <v>6822719</v>
+        <v>6822797</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,10 +2733,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117711735</v>
+        <v>117711459</v>
       </c>
       <c r="B22" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,37 +2749,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465135</v>
+        <v>465193</v>
       </c>
       <c r="R22" t="n">
-        <v>6822833</v>
+        <v>6822569</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2805,18 +2811,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2835,10 +2835,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117711904</v>
+        <v>117711833</v>
       </c>
       <c r="B23" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465051</v>
+        <v>465310</v>
       </c>
       <c r="R23" t="n">
-        <v>6822914</v>
+        <v>6822472</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117711881</v>
+        <v>117711761</v>
       </c>
       <c r="B24" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465010</v>
+        <v>465039</v>
       </c>
       <c r="R24" t="n">
-        <v>6823186</v>
+        <v>6822657</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117711483</v>
+        <v>117711697</v>
       </c>
       <c r="B25" t="n">
-        <v>79098</v>
+        <v>78218</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3055,21 +3055,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464993</v>
+        <v>465233</v>
       </c>
       <c r="R25" t="n">
-        <v>6823209</v>
+        <v>6822515</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,10 +3141,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117711711</v>
+        <v>117711868</v>
       </c>
       <c r="B26" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3157,21 +3157,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465071</v>
+        <v>464976</v>
       </c>
       <c r="R26" t="n">
-        <v>6822963</v>
+        <v>6823119</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3243,10 +3243,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117711468</v>
+        <v>117711543</v>
       </c>
       <c r="B27" t="n">
-        <v>79098</v>
+        <v>56500</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3255,38 +3255,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465151</v>
+        <v>465107</v>
       </c>
       <c r="R27" t="n">
-        <v>6822788</v>
+        <v>6822869</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3345,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117711853</v>
+        <v>117711403</v>
       </c>
       <c r="B28" t="n">
-        <v>78480</v>
+        <v>78516</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3361,21 +3373,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3385,10 +3397,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465129</v>
+        <v>465258</v>
       </c>
       <c r="R28" t="n">
-        <v>6822859</v>
+        <v>6822486</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3447,10 +3459,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117711861</v>
+        <v>117711470</v>
       </c>
       <c r="B29" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3463,21 +3475,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3487,10 +3499,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465018</v>
+        <v>465099</v>
       </c>
       <c r="R29" t="n">
-        <v>6823007</v>
+        <v>6822897</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3549,10 +3561,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117711773</v>
+        <v>117711846</v>
       </c>
       <c r="B30" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3589,10 +3601,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465256</v>
+        <v>465149</v>
       </c>
       <c r="R30" t="n">
-        <v>6822710</v>
+        <v>6822795</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3651,10 +3663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117711899</v>
+        <v>117711491</v>
       </c>
       <c r="B31" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3667,21 +3679,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3691,10 +3703,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465008</v>
+        <v>465043</v>
       </c>
       <c r="R31" t="n">
-        <v>6822955</v>
+        <v>6823043</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3753,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117711492</v>
+        <v>117711739</v>
       </c>
       <c r="B32" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3769,21 +3781,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3793,10 +3805,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465025</v>
+        <v>465429</v>
       </c>
       <c r="R32" t="n">
-        <v>6822860</v>
+        <v>6822519</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3855,10 +3867,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117711476</v>
+        <v>117711905</v>
       </c>
       <c r="B33" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3871,21 +3883,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3895,10 +3907,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465003</v>
+        <v>465056</v>
       </c>
       <c r="R33" t="n">
-        <v>6823046</v>
+        <v>6822904</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3957,10 +3969,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117711995</v>
+        <v>117711486</v>
       </c>
       <c r="B34" t="n">
-        <v>78125</v>
+        <v>79100</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3973,21 +3985,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3997,10 +4009,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465043</v>
+        <v>465056</v>
       </c>
       <c r="R34" t="n">
-        <v>6822986</v>
+        <v>6823106</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4059,10 +4071,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117711827</v>
+        <v>117711904</v>
       </c>
       <c r="B35" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4099,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465273</v>
+        <v>465051</v>
       </c>
       <c r="R35" t="n">
-        <v>6822555</v>
+        <v>6822914</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4161,10 +4173,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117711831</v>
+        <v>117711698</v>
       </c>
       <c r="B36" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4177,21 +4189,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4201,10 +4213,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465280</v>
+        <v>465299</v>
       </c>
       <c r="R36" t="n">
-        <v>6822526</v>
+        <v>6822674</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4263,10 +4275,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117711761</v>
+        <v>117711914</v>
       </c>
       <c r="B37" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4303,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465039</v>
+        <v>465107</v>
       </c>
       <c r="R37" t="n">
-        <v>6822657</v>
+        <v>6822816</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4365,10 +4377,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117711771</v>
+        <v>117711708</v>
       </c>
       <c r="B38" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4381,21 +4393,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4405,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465314</v>
+        <v>465185</v>
       </c>
       <c r="R38" t="n">
-        <v>6822659</v>
+        <v>6822623</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4467,10 +4479,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117711562</v>
+        <v>117711858</v>
       </c>
       <c r="B39" t="n">
-        <v>79590</v>
+        <v>78482</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4479,41 +4491,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465330</v>
+        <v>465091</v>
       </c>
       <c r="R39" t="n">
-        <v>6822497</v>
+        <v>6822883</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4548,18 +4557,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4578,10 +4581,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117711611</v>
+        <v>117711792</v>
       </c>
       <c r="B40" t="n">
-        <v>78506</v>
+        <v>78482</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4590,25 +4593,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4618,10 +4621,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465028</v>
+        <v>465033</v>
       </c>
       <c r="R40" t="n">
-        <v>6823122</v>
+        <v>6823207</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4680,10 +4683,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117711555</v>
+        <v>117711852</v>
       </c>
       <c r="B41" t="n">
-        <v>79590</v>
+        <v>78482</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4692,41 +4695,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464989</v>
+        <v>465132</v>
       </c>
       <c r="R41" t="n">
-        <v>6822826</v>
+        <v>6822856</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4761,18 +4761,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På rönn</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4791,10 +4785,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117711909</v>
+        <v>117711862</v>
       </c>
       <c r="B42" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4831,10 +4825,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465054</v>
+        <v>464996</v>
       </c>
       <c r="R42" t="n">
-        <v>6822855</v>
+        <v>6823076</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4893,10 +4887,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117711480</v>
+        <v>117711485</v>
       </c>
       <c r="B43" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4933,10 +4927,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464969</v>
+        <v>465022</v>
       </c>
       <c r="R43" t="n">
-        <v>6823166</v>
+        <v>6823158</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4995,10 +4989,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117711525</v>
+        <v>117711866</v>
       </c>
       <c r="B44" t="n">
-        <v>79069</v>
+        <v>78482</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5011,21 +5005,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5035,10 +5029,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465045</v>
+        <v>464983</v>
       </c>
       <c r="R44" t="n">
-        <v>6823044</v>
+        <v>6823097</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5100,7 +5094,7 @@
         <v>117711587</v>
       </c>
       <c r="B45" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5199,10 +5193,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117711905</v>
+        <v>117711439</v>
       </c>
       <c r="B46" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5215,21 +5209,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5239,10 +5233,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465056</v>
+        <v>465238</v>
       </c>
       <c r="R46" t="n">
-        <v>6822904</v>
+        <v>6822512</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5301,10 +5295,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117711778</v>
+        <v>117711926</v>
       </c>
       <c r="B47" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5341,10 +5335,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465229</v>
+        <v>464988</v>
       </c>
       <c r="R47" t="n">
-        <v>6822789</v>
+        <v>6822780</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5403,10 +5397,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117711777</v>
+        <v>117711383</v>
       </c>
       <c r="B48" t="n">
-        <v>78480</v>
+        <v>74594</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5419,21 +5413,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5443,10 +5437,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465234</v>
+        <v>465251</v>
       </c>
       <c r="R48" t="n">
-        <v>6822786</v>
+        <v>6822507</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5505,10 +5499,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117711609</v>
+        <v>117711773</v>
       </c>
       <c r="B49" t="n">
-        <v>78506</v>
+        <v>78482</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5517,25 +5511,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5545,10 +5539,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465379</v>
+        <v>465256</v>
       </c>
       <c r="R49" t="n">
-        <v>6822539</v>
+        <v>6822710</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5607,10 +5601,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117711491</v>
+        <v>117711928</v>
       </c>
       <c r="B50" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5623,21 +5617,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5647,10 +5641,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465043</v>
+        <v>464986</v>
       </c>
       <c r="R50" t="n">
-        <v>6823043</v>
+        <v>6822795</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5709,10 +5703,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117711675</v>
+        <v>117711652</v>
       </c>
       <c r="B51" t="n">
-        <v>79561</v>
+        <v>78219</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5725,21 +5719,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5749,10 +5743,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465115</v>
+        <v>465407</v>
       </c>
       <c r="R51" t="n">
-        <v>6822797</v>
+        <v>6822454</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5811,10 +5805,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117711416</v>
+        <v>117711903</v>
       </c>
       <c r="B52" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5827,21 +5821,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5851,10 +5845,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465431</v>
+        <v>465035</v>
       </c>
       <c r="R52" t="n">
-        <v>6822517</v>
+        <v>6822922</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5913,10 +5907,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117711862</v>
+        <v>117711696</v>
       </c>
       <c r="B53" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5929,21 +5923,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5953,10 +5947,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464996</v>
+        <v>465187</v>
       </c>
       <c r="R53" t="n">
-        <v>6823076</v>
+        <v>6822623</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6015,10 +6009,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117711779</v>
+        <v>117711827</v>
       </c>
       <c r="B54" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6055,10 +6049,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465222</v>
+        <v>465273</v>
       </c>
       <c r="R54" t="n">
-        <v>6822812</v>
+        <v>6822555</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6117,10 +6111,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117711699</v>
+        <v>117711610</v>
       </c>
       <c r="B55" t="n">
-        <v>78216</v>
+        <v>78508</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6129,25 +6123,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6157,10 +6151,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465258</v>
+        <v>465212</v>
       </c>
       <c r="R55" t="n">
-        <v>6822743</v>
+        <v>6822555</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6219,10 +6213,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117711484</v>
+        <v>117711625</v>
       </c>
       <c r="B56" t="n">
-        <v>79098</v>
+        <v>78219</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6235,21 +6229,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6259,10 +6253,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465012</v>
+        <v>465407</v>
       </c>
       <c r="R56" t="n">
-        <v>6823194</v>
+        <v>6822451</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6321,10 +6315,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117711730</v>
+        <v>117711993</v>
       </c>
       <c r="B57" t="n">
-        <v>90648</v>
+        <v>78127</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6333,25 +6327,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6361,10 +6355,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465146</v>
+        <v>465056</v>
       </c>
       <c r="R57" t="n">
-        <v>6822800</v>
+        <v>6823075</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6423,10 +6417,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117711729</v>
+        <v>117711555</v>
       </c>
       <c r="B58" t="n">
-        <v>90648</v>
+        <v>79592</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6435,38 +6429,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465321</v>
+        <v>464989</v>
       </c>
       <c r="R58" t="n">
-        <v>6822500</v>
+        <v>6822826</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6501,12 +6498,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6525,10 +6528,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117711619</v>
+        <v>117711908</v>
       </c>
       <c r="B59" t="n">
-        <v>79589</v>
+        <v>78482</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6537,25 +6540,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6565,10 +6568,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465021</v>
+        <v>465045</v>
       </c>
       <c r="R59" t="n">
-        <v>6822978</v>
+        <v>6822855</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6627,10 +6630,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117711487</v>
+        <v>117711717</v>
       </c>
       <c r="B60" t="n">
-        <v>79098</v>
+        <v>78218</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6643,21 +6646,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6667,10 +6670,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465063</v>
+        <v>465056</v>
       </c>
       <c r="R60" t="n">
-        <v>6823088</v>
+        <v>6822933</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6729,10 +6732,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117711494</v>
+        <v>117711489</v>
       </c>
       <c r="B61" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6769,10 +6772,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465042</v>
+        <v>465056</v>
       </c>
       <c r="R61" t="n">
-        <v>6822770</v>
+        <v>6823075</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6831,10 +6834,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117711408</v>
+        <v>117711869</v>
       </c>
       <c r="B62" t="n">
-        <v>78514</v>
+        <v>78482</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6847,21 +6850,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6871,10 +6874,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465002</v>
+        <v>464963</v>
       </c>
       <c r="R62" t="n">
-        <v>6823046</v>
+        <v>6823132</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6933,10 +6936,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117711897</v>
+        <v>117711474</v>
       </c>
       <c r="B63" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6949,21 +6952,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6973,10 +6976,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465002</v>
+        <v>465026</v>
       </c>
       <c r="R63" t="n">
-        <v>6822972</v>
+        <v>6823006</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7035,10 +7038,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117711903</v>
+        <v>117711494</v>
       </c>
       <c r="B64" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7051,21 +7054,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7075,10 +7078,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465035</v>
+        <v>465042</v>
       </c>
       <c r="R64" t="n">
-        <v>6822922</v>
+        <v>6822770</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7137,10 +7140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117711843</v>
+        <v>117711873</v>
       </c>
       <c r="B65" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7177,10 +7180,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465110</v>
+        <v>464912</v>
       </c>
       <c r="R65" t="n">
-        <v>6822717</v>
+        <v>6823140</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7239,10 +7242,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117711734</v>
+        <v>117711736</v>
       </c>
       <c r="B66" t="n">
-        <v>90517</v>
+        <v>78482</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7255,21 +7258,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7282,10 +7285,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465126</v>
+        <v>465029</v>
       </c>
       <c r="R66" t="n">
-        <v>6822834</v>
+        <v>6823165</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7322,7 +7325,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Mitt i planerad körväg</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7350,10 +7353,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117711764</v>
+        <v>117711929</v>
       </c>
       <c r="B67" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7390,10 +7393,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465109</v>
+        <v>464985</v>
       </c>
       <c r="R67" t="n">
-        <v>6822696</v>
+        <v>6822805</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7452,10 +7455,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117711930</v>
+        <v>117711834</v>
       </c>
       <c r="B68" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7492,10 +7495,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464991</v>
+        <v>465301</v>
       </c>
       <c r="R68" t="n">
-        <v>6822809</v>
+        <v>6822474</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7554,10 +7557,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117711651</v>
+        <v>117711867</v>
       </c>
       <c r="B69" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7570,21 +7573,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7594,10 +7597,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465187</v>
+        <v>464978</v>
       </c>
       <c r="R69" t="n">
-        <v>6822613</v>
+        <v>6823101</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7656,10 +7659,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117711656</v>
+        <v>117711769</v>
       </c>
       <c r="B70" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7672,21 +7675,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7696,10 +7699,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465183</v>
+        <v>465379</v>
       </c>
       <c r="R70" t="n">
-        <v>6822626</v>
+        <v>6822539</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7758,10 +7761,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117711991</v>
+        <v>117711778</v>
       </c>
       <c r="B71" t="n">
-        <v>78125</v>
+        <v>78482</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7774,21 +7777,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7798,10 +7801,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465046</v>
+        <v>465229</v>
       </c>
       <c r="R71" t="n">
-        <v>6823084</v>
+        <v>6822789</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7860,10 +7863,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117711894</v>
+        <v>117711994</v>
       </c>
       <c r="B72" t="n">
-        <v>78480</v>
+        <v>78127</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7876,21 +7879,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7900,10 +7903,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465032</v>
+        <v>465054</v>
       </c>
       <c r="R72" t="n">
-        <v>6822993</v>
+        <v>6823006</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7962,10 +7965,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117711889</v>
+        <v>117711406</v>
       </c>
       <c r="B73" t="n">
-        <v>78480</v>
+        <v>78516</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7978,21 +7981,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8002,10 +8005,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465072</v>
+        <v>465008</v>
       </c>
       <c r="R73" t="n">
-        <v>6823099</v>
+        <v>6823044</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8064,10 +8067,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117711739</v>
+        <v>117711562</v>
       </c>
       <c r="B74" t="n">
-        <v>78480</v>
+        <v>79592</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8076,38 +8079,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465429</v>
+        <v>465330</v>
       </c>
       <c r="R74" t="n">
-        <v>6822519</v>
+        <v>6822497</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8142,12 +8148,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8166,10 +8178,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117711876</v>
+        <v>117711699</v>
       </c>
       <c r="B75" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8182,21 +8194,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8206,10 +8218,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464928</v>
+        <v>465258</v>
       </c>
       <c r="R75" t="n">
-        <v>6823159</v>
+        <v>6822743</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8268,10 +8280,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117711922</v>
+        <v>117711916</v>
       </c>
       <c r="B76" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8308,10 +8320,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465084</v>
+        <v>465096</v>
       </c>
       <c r="R76" t="n">
-        <v>6822769</v>
+        <v>6822795</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8370,10 +8382,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117711765</v>
+        <v>117711823</v>
       </c>
       <c r="B77" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8410,10 +8422,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465105</v>
+        <v>465157</v>
       </c>
       <c r="R77" t="n">
-        <v>6822680</v>
+        <v>6822719</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8472,10 +8484,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117711824</v>
+        <v>117711612</v>
       </c>
       <c r="B78" t="n">
-        <v>78480</v>
+        <v>78508</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8484,25 +8496,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8512,10 +8524,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>465160</v>
+        <v>465019</v>
       </c>
       <c r="R78" t="n">
-        <v>6822693</v>
+        <v>6822780</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8574,10 +8586,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117711868</v>
+        <v>117711856</v>
       </c>
       <c r="B79" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8614,10 +8626,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464976</v>
+        <v>465118</v>
       </c>
       <c r="R79" t="n">
-        <v>6823119</v>
+        <v>6822876</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8676,10 +8688,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117711879</v>
+        <v>117711700</v>
       </c>
       <c r="B80" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8692,21 +8704,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8716,10 +8728,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464980</v>
+        <v>465104</v>
       </c>
       <c r="R80" t="n">
-        <v>6823196</v>
+        <v>6823045</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8778,10 +8790,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117711825</v>
+        <v>117711850</v>
       </c>
       <c r="B81" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8818,10 +8830,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465178</v>
+        <v>465139</v>
       </c>
       <c r="R81" t="n">
-        <v>6822682</v>
+        <v>6822842</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8880,10 +8892,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117711713</v>
+        <v>117711909</v>
       </c>
       <c r="B82" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8896,21 +8908,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8920,10 +8932,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>465046</v>
+        <v>465054</v>
       </c>
       <c r="R82" t="n">
-        <v>6823046</v>
+        <v>6822855</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8982,10 +8994,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117711697</v>
+        <v>117711915</v>
       </c>
       <c r="B83" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8998,21 +9010,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9022,10 +9034,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>465233</v>
+        <v>465102</v>
       </c>
       <c r="R83" t="n">
-        <v>6822515</v>
+        <v>6822788</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9084,10 +9096,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117711470</v>
+        <v>117711405</v>
       </c>
       <c r="B84" t="n">
-        <v>79098</v>
+        <v>78516</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9100,21 +9112,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9124,10 +9136,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>465099</v>
+        <v>465016</v>
       </c>
       <c r="R84" t="n">
-        <v>6822897</v>
+        <v>6823015</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9186,10 +9198,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117711486</v>
+        <v>117711523</v>
       </c>
       <c r="B85" t="n">
-        <v>79098</v>
+        <v>79071</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9202,21 +9214,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9229,7 +9241,7 @@
         <v>465056</v>
       </c>
       <c r="R85" t="n">
-        <v>6823106</v>
+        <v>6823105</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9288,10 +9300,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117711438</v>
+        <v>117711477</v>
       </c>
       <c r="B86" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9328,10 +9340,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>465187</v>
+        <v>464973</v>
       </c>
       <c r="R86" t="n">
-        <v>6822623</v>
+        <v>6823110</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9390,10 +9402,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117711458</v>
+        <v>117711484</v>
       </c>
       <c r="B87" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9430,10 +9442,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>465184</v>
+        <v>465012</v>
       </c>
       <c r="R87" t="n">
-        <v>6822626</v>
+        <v>6823194</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9492,10 +9504,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117711869</v>
+        <v>117711438</v>
       </c>
       <c r="B88" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9508,21 +9520,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9532,10 +9544,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464963</v>
+        <v>465187</v>
       </c>
       <c r="R88" t="n">
-        <v>6823132</v>
+        <v>6822623</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9594,10 +9606,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117711493</v>
+        <v>117711879</v>
       </c>
       <c r="B89" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9610,21 +9622,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9634,10 +9646,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>465091</v>
+        <v>464980</v>
       </c>
       <c r="R89" t="n">
-        <v>6822828</v>
+        <v>6823196</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9696,10 +9708,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117711537</v>
+        <v>117711619</v>
       </c>
       <c r="B90" t="n">
-        <v>57287</v>
+        <v>79591</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9708,46 +9720,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>465167</v>
+        <v>465021</v>
       </c>
       <c r="R90" t="n">
-        <v>6822725</v>
+        <v>6822978</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9806,10 +9810,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117711891</v>
+        <v>117711620</v>
       </c>
       <c r="B91" t="n">
-        <v>78480</v>
+        <v>79591</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9818,25 +9822,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9846,10 +9850,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>465027</v>
+        <v>465060</v>
       </c>
       <c r="R91" t="n">
-        <v>6823022</v>
+        <v>6822839</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9908,10 +9912,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117711907</v>
+        <v>117711764</v>
       </c>
       <c r="B92" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9948,10 +9952,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>465022</v>
+        <v>465109</v>
       </c>
       <c r="R92" t="n">
-        <v>6822851</v>
+        <v>6822696</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10010,10 +10014,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117711858</v>
+        <v>117711729</v>
       </c>
       <c r="B93" t="n">
-        <v>78480</v>
+        <v>90650</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10022,25 +10026,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10050,10 +10054,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>465091</v>
+        <v>465321</v>
       </c>
       <c r="R93" t="n">
-        <v>6822883</v>
+        <v>6822500</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10112,10 +10116,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117711926</v>
+        <v>117711525</v>
       </c>
       <c r="B94" t="n">
-        <v>78480</v>
+        <v>79071</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10128,21 +10132,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10152,10 +10156,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464988</v>
+        <v>465045</v>
       </c>
       <c r="R94" t="n">
-        <v>6822780</v>
+        <v>6823044</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10214,10 +10218,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117711866</v>
+        <v>117711674</v>
       </c>
       <c r="B95" t="n">
-        <v>78480</v>
+        <v>79563</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10230,21 +10234,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10254,10 +10258,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464983</v>
+        <v>465071</v>
       </c>
       <c r="R95" t="n">
-        <v>6823097</v>
+        <v>6822839</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10316,10 +10320,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117711916</v>
+        <v>117711919</v>
       </c>
       <c r="B96" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10356,10 +10360,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>465096</v>
+        <v>465081</v>
       </c>
       <c r="R96" t="n">
-        <v>6822795</v>
+        <v>6822777</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10418,10 +10422,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117711625</v>
+        <v>117711848</v>
       </c>
       <c r="B97" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10434,21 +10438,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10458,10 +10462,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465407</v>
+        <v>465126</v>
       </c>
       <c r="R97" t="n">
-        <v>6822451</v>
+        <v>6822829</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10520,10 +10524,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117711662</v>
+        <v>117711396</v>
       </c>
       <c r="B98" t="n">
-        <v>78217</v>
+        <v>78516</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10536,21 +10540,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10560,10 +10564,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465042</v>
+        <v>465249</v>
       </c>
       <c r="R98" t="n">
-        <v>6822770</v>
+        <v>6822748</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10622,10 +10626,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117711698</v>
+        <v>117711661</v>
       </c>
       <c r="B99" t="n">
-        <v>78216</v>
+        <v>78219</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10638,21 +10642,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10662,10 +10666,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465299</v>
+        <v>465051</v>
       </c>
       <c r="R99" t="n">
-        <v>6822674</v>
+        <v>6822925</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10724,10 +10728,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117711766</v>
+        <v>117711927</v>
       </c>
       <c r="B100" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10764,10 +10768,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465122</v>
+        <v>464979</v>
       </c>
       <c r="R100" t="n">
-        <v>6822673</v>
+        <v>6822792</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10826,10 +10830,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>117711462</v>
+        <v>117711895</v>
       </c>
       <c r="B101" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10842,21 +10846,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10866,10 +10870,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>465290</v>
+        <v>465019</v>
       </c>
       <c r="R101" t="n">
-        <v>6822535</v>
+        <v>6822976</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10928,10 +10932,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117711612</v>
+        <v>117711922</v>
       </c>
       <c r="B102" t="n">
-        <v>78506</v>
+        <v>78482</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10940,25 +10944,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10968,10 +10972,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>465019</v>
+        <v>465084</v>
       </c>
       <c r="R102" t="n">
-        <v>6822780</v>
+        <v>6822769</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11030,10 +11034,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117711403</v>
+        <v>117711826</v>
       </c>
       <c r="B103" t="n">
-        <v>78514</v>
+        <v>78482</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11046,21 +11050,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11070,10 +11074,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>465258</v>
+        <v>465192</v>
       </c>
       <c r="R103" t="n">
-        <v>6822486</v>
+        <v>6822668</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11132,10 +11136,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>117711846</v>
+        <v>117711843</v>
       </c>
       <c r="B104" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11172,10 +11176,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>465149</v>
+        <v>465110</v>
       </c>
       <c r="R104" t="n">
-        <v>6822795</v>
+        <v>6822717</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11234,10 +11238,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>117711852</v>
+        <v>117711880</v>
       </c>
       <c r="B105" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11274,10 +11278,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>465132</v>
+        <v>465011</v>
       </c>
       <c r="R105" t="n">
-        <v>6822856</v>
+        <v>6823194</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11336,10 +11340,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>117711822</v>
+        <v>117711735</v>
       </c>
       <c r="B106" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11370,16 +11374,19 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>465170</v>
+        <v>465135</v>
       </c>
       <c r="R106" t="n">
-        <v>6822724</v>
+        <v>6822833</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11414,12 +11421,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11438,10 +11451,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>117711829</v>
+        <v>117711913</v>
       </c>
       <c r="B107" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11478,10 +11491,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>465274</v>
+        <v>465106</v>
       </c>
       <c r="R107" t="n">
-        <v>6822528</v>
+        <v>6822818</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11540,10 +11553,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>117711736</v>
+        <v>117711824</v>
       </c>
       <c r="B108" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11574,19 +11587,16 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>465029</v>
+        <v>465160</v>
       </c>
       <c r="R108" t="n">
-        <v>6823165</v>
+        <v>6822693</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11621,18 +11631,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11651,10 +11655,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>117711912</v>
+        <v>117711897</v>
       </c>
       <c r="B109" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11691,10 +11695,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>465072</v>
+        <v>465002</v>
       </c>
       <c r="R109" t="n">
-        <v>6822834</v>
+        <v>6822972</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11753,10 +11757,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>117711769</v>
+        <v>117711483</v>
       </c>
       <c r="B110" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11769,21 +11773,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11793,10 +11797,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>465379</v>
+        <v>464993</v>
       </c>
       <c r="R110" t="n">
-        <v>6822539</v>
+        <v>6823209</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11855,10 +11859,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>117711867</v>
+        <v>117711881</v>
       </c>
       <c r="B111" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11895,10 +11899,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464978</v>
+        <v>465010</v>
       </c>
       <c r="R111" t="n">
-        <v>6823101</v>
+        <v>6823186</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11957,10 +11961,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>117711919</v>
+        <v>117711829</v>
       </c>
       <c r="B112" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11997,10 +12001,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465081</v>
+        <v>465274</v>
       </c>
       <c r="R112" t="n">
-        <v>6822777</v>
+        <v>6822528</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12059,10 +12063,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>117711880</v>
+        <v>117711462</v>
       </c>
       <c r="B113" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12075,21 +12079,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12099,10 +12103,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>465011</v>
+        <v>465290</v>
       </c>
       <c r="R113" t="n">
-        <v>6823194</v>
+        <v>6822535</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12161,10 +12165,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>117711473</v>
+        <v>117711480</v>
       </c>
       <c r="B114" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12201,10 +12205,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>465065</v>
+        <v>464969</v>
       </c>
       <c r="R114" t="n">
-        <v>6822969</v>
+        <v>6823166</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12263,10 +12267,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>117711847</v>
+        <v>117711732</v>
       </c>
       <c r="B115" t="n">
-        <v>78480</v>
+        <v>79608</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12279,21 +12283,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>229504</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12303,10 +12307,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>465136</v>
+        <v>465042</v>
       </c>
       <c r="R115" t="n">
-        <v>6822815</v>
+        <v>6822859</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12365,10 +12369,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>117711672</v>
+        <v>117711407</v>
       </c>
       <c r="B116" t="n">
-        <v>96797</v>
+        <v>78516</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12377,25 +12381,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12405,10 +12409,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464987</v>
+        <v>465007</v>
       </c>
       <c r="R116" t="n">
-        <v>6823079</v>
+        <v>6823041</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12467,10 +12471,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>117711875</v>
+        <v>117712003</v>
       </c>
       <c r="B117" t="n">
-        <v>78480</v>
+        <v>91774</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12479,25 +12483,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12507,10 +12511,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464916</v>
+        <v>465272</v>
       </c>
       <c r="R117" t="n">
-        <v>6823144</v>
+        <v>6822559</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12569,10 +12573,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>117711834</v>
+        <v>117711712</v>
       </c>
       <c r="B118" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12585,21 +12589,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12609,10 +12613,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>465301</v>
+        <v>465057</v>
       </c>
       <c r="R118" t="n">
-        <v>6822474</v>
+        <v>6823105</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12671,10 +12675,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>117711920</v>
+        <v>117711786</v>
       </c>
       <c r="B119" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12711,10 +12715,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>465088</v>
+        <v>465086</v>
       </c>
       <c r="R119" t="n">
-        <v>6822770</v>
+        <v>6823030</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12773,10 +12777,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>117711925</v>
+        <v>117711877</v>
       </c>
       <c r="B120" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12813,10 +12817,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465019</v>
+        <v>464928</v>
       </c>
       <c r="R120" t="n">
-        <v>6822782</v>
+        <v>6823159</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12875,10 +12879,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>117711717</v>
+        <v>117711890</v>
       </c>
       <c r="B121" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12891,21 +12895,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12915,10 +12919,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>465056</v>
+        <v>465064</v>
       </c>
       <c r="R121" t="n">
-        <v>6822933</v>
+        <v>6823106</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12977,10 +12981,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>117711482</v>
+        <v>117711768</v>
       </c>
       <c r="B122" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12993,21 +12997,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13017,10 +13021,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464989</v>
+        <v>465394</v>
       </c>
       <c r="R122" t="n">
-        <v>6823223</v>
+        <v>6822493</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13079,10 +13083,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>117711472</v>
+        <v>117711888</v>
       </c>
       <c r="B123" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13095,21 +13099,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13119,10 +13123,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>465070</v>
+        <v>465030</v>
       </c>
       <c r="R123" t="n">
-        <v>6822961</v>
+        <v>6823125</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13181,10 +13185,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>117711661</v>
+        <v>117711611</v>
       </c>
       <c r="B124" t="n">
-        <v>78217</v>
+        <v>78508</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13193,25 +13197,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13221,10 +13225,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>465051</v>
+        <v>465028</v>
       </c>
       <c r="R124" t="n">
-        <v>6822925</v>
+        <v>6823122</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13283,10 +13287,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>117711785</v>
+        <v>117711893</v>
       </c>
       <c r="B125" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13323,10 +13327,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>465096</v>
+        <v>465052</v>
       </c>
       <c r="R125" t="n">
-        <v>6823017</v>
+        <v>6823002</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13385,10 +13389,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>117711883</v>
+        <v>117711713</v>
       </c>
       <c r="B126" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13401,21 +13405,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13425,10 +13429,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>465030</v>
+        <v>465046</v>
       </c>
       <c r="R126" t="n">
-        <v>6823162</v>
+        <v>6823046</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13487,10 +13491,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>117711929</v>
+        <v>117711660</v>
       </c>
       <c r="B127" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13503,21 +13507,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13527,10 +13531,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>464985</v>
+        <v>465045</v>
       </c>
       <c r="R127" t="n">
-        <v>6822805</v>
+        <v>6823044</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13589,10 +13593,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>117711918</v>
+        <v>117711716</v>
       </c>
       <c r="B128" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13605,21 +13609,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13629,10 +13633,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>465083</v>
+        <v>465050</v>
       </c>
       <c r="R128" t="n">
-        <v>6822781</v>
+        <v>6822991</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13691,10 +13695,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>117711927</v>
+        <v>117711872</v>
       </c>
       <c r="B129" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13731,10 +13735,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464979</v>
+        <v>464915</v>
       </c>
       <c r="R129" t="n">
-        <v>6822792</v>
+        <v>6823136</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13793,10 +13797,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>117711475</v>
+        <v>117711476</v>
       </c>
       <c r="B130" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13836,7 +13840,7 @@
         <v>465003</v>
       </c>
       <c r="R130" t="n">
-        <v>6823040</v>
+        <v>6823046</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13895,10 +13899,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>117711383</v>
+        <v>117711990</v>
       </c>
       <c r="B131" t="n">
-        <v>74592</v>
+        <v>78127</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13911,21 +13915,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13935,10 +13939,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>465251</v>
+        <v>464988</v>
       </c>
       <c r="R131" t="n">
-        <v>6822507</v>
+        <v>6823222</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13997,10 +14001,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>117711402</v>
+        <v>117711537</v>
       </c>
       <c r="B132" t="n">
-        <v>78514</v>
+        <v>57288</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14013,34 +14017,42 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>465170</v>
+        <v>465167</v>
       </c>
       <c r="R132" t="n">
-        <v>6822729</v>
+        <v>6822725</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14099,10 +14111,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>117711990</v>
+        <v>117711830</v>
       </c>
       <c r="B133" t="n">
-        <v>78125</v>
+        <v>78482</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14115,21 +14127,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14139,10 +14151,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464988</v>
+        <v>465282</v>
       </c>
       <c r="R133" t="n">
-        <v>6823222</v>
+        <v>6822525</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14201,10 +14213,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>117711738</v>
+        <v>117711487</v>
       </c>
       <c r="B134" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14217,21 +14229,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14241,10 +14253,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>465426</v>
+        <v>465063</v>
       </c>
       <c r="R134" t="n">
-        <v>6822469</v>
+        <v>6823088</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14303,10 +14315,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>117711914</v>
+        <v>117711779</v>
       </c>
       <c r="B135" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14343,10 +14355,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>465107</v>
+        <v>465222</v>
       </c>
       <c r="R135" t="n">
-        <v>6822816</v>
+        <v>6822812</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14405,10 +14417,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>117711842</v>
+        <v>117711924</v>
       </c>
       <c r="B136" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14445,10 +14457,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>465106</v>
+        <v>465032</v>
       </c>
       <c r="R136" t="n">
-        <v>6822702</v>
+        <v>6822777</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14507,10 +14519,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>117711865</v>
+        <v>117711861</v>
       </c>
       <c r="B137" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14547,10 +14559,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464973</v>
+        <v>465018</v>
       </c>
       <c r="R137" t="n">
-        <v>6823085</v>
+        <v>6823007</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14609,10 +14621,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>117711911</v>
+        <v>117711479</v>
       </c>
       <c r="B138" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14625,21 +14637,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14649,10 +14661,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>465059</v>
+        <v>464928</v>
       </c>
       <c r="R138" t="n">
-        <v>6822842</v>
+        <v>6823159</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14711,10 +14723,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>117711915</v>
+        <v>117711458</v>
       </c>
       <c r="B139" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14727,21 +14739,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14751,10 +14763,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>465102</v>
+        <v>465184</v>
       </c>
       <c r="R139" t="n">
-        <v>6822788</v>
+        <v>6822626</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14813,10 +14825,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>117712003</v>
+        <v>117711772</v>
       </c>
       <c r="B140" t="n">
-        <v>91772</v>
+        <v>78482</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14825,25 +14837,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14853,10 +14865,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>465272</v>
+        <v>465258</v>
       </c>
       <c r="R140" t="n">
-        <v>6822559</v>
+        <v>6822696</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14915,10 +14927,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>117711917</v>
+        <v>117711765</v>
       </c>
       <c r="B141" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14955,10 +14967,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>465092</v>
+        <v>465105</v>
       </c>
       <c r="R141" t="n">
-        <v>6822793</v>
+        <v>6822680</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15017,10 +15029,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>117711708</v>
+        <v>117711482</v>
       </c>
       <c r="B142" t="n">
-        <v>78216</v>
+        <v>79100</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15033,21 +15045,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15057,10 +15069,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>465185</v>
+        <v>464989</v>
       </c>
       <c r="R142" t="n">
-        <v>6822623</v>
+        <v>6823223</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15119,10 +15131,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>117711715</v>
+        <v>117711882</v>
       </c>
       <c r="B143" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15135,21 +15147,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15159,10 +15171,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>465052</v>
+        <v>465023</v>
       </c>
       <c r="R143" t="n">
-        <v>6823001</v>
+        <v>6823173</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15221,10 +15233,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>117711923</v>
+        <v>117711889</v>
       </c>
       <c r="B144" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15261,10 +15273,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>465060</v>
+        <v>465072</v>
       </c>
       <c r="R144" t="n">
-        <v>6822763</v>
+        <v>6823099</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15323,10 +15335,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>117711586</v>
+        <v>117711731</v>
       </c>
       <c r="B145" t="n">
-        <v>79562</v>
+        <v>90650</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15335,25 +15347,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2081</v>
+        <v>1503</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15363,10 +15375,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>465034</v>
+        <v>465012</v>
       </c>
       <c r="R145" t="n">
-        <v>6822859</v>
+        <v>6823041</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15425,10 +15437,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>117711477</v>
+        <v>117711845</v>
       </c>
       <c r="B146" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15441,21 +15453,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15465,10 +15477,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>464973</v>
+        <v>465139</v>
       </c>
       <c r="R146" t="n">
-        <v>6823110</v>
+        <v>6822785</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15527,10 +15539,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>117711674</v>
+        <v>117711467</v>
       </c>
       <c r="B147" t="n">
-        <v>79561</v>
+        <v>79100</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15543,21 +15555,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15567,10 +15579,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>465071</v>
+        <v>465057</v>
       </c>
       <c r="R147" t="n">
-        <v>6822839</v>
+        <v>6822708</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15629,10 +15641,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>117711489</v>
+        <v>117711899</v>
       </c>
       <c r="B148" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15645,21 +15657,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15669,10 +15681,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>465056</v>
+        <v>465008</v>
       </c>
       <c r="R148" t="n">
-        <v>6823075</v>
+        <v>6822955</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15731,10 +15743,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>117711716</v>
+        <v>117711608</v>
       </c>
       <c r="B149" t="n">
-        <v>78216</v>
+        <v>78508</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15743,25 +15755,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15771,10 +15783,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>465050</v>
+        <v>465207</v>
       </c>
       <c r="R149" t="n">
-        <v>6822991</v>
+        <v>6822564</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15833,10 +15845,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>117711523</v>
+        <v>117711911</v>
       </c>
       <c r="B150" t="n">
-        <v>79069</v>
+        <v>78482</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15849,21 +15861,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15873,10 +15885,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>465056</v>
+        <v>465059</v>
       </c>
       <c r="R150" t="n">
-        <v>6823105</v>
+        <v>6822842</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15935,10 +15947,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>117711657</v>
+        <v>117711461</v>
       </c>
       <c r="B151" t="n">
-        <v>78217</v>
+        <v>79100</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15951,21 +15963,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15975,10 +15987,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>465059</v>
+        <v>465276</v>
       </c>
       <c r="R151" t="n">
-        <v>6822705</v>
+        <v>6822556</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16037,10 +16049,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>117711404</v>
+        <v>117711416</v>
       </c>
       <c r="B152" t="n">
-        <v>78514</v>
+        <v>79100</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16053,21 +16065,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16077,10 +16089,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>465098</v>
+        <v>465431</v>
       </c>
       <c r="R152" t="n">
-        <v>6822909</v>
+        <v>6822517</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16139,10 +16151,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>117711405</v>
+        <v>117711930</v>
       </c>
       <c r="B153" t="n">
-        <v>78514</v>
+        <v>78482</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16155,21 +16167,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16179,10 +16191,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>465016</v>
+        <v>464991</v>
       </c>
       <c r="R153" t="n">
-        <v>6823015</v>
+        <v>6822809</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16241,10 +16253,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>117712007</v>
+        <v>117711884</v>
       </c>
       <c r="B154" t="n">
-        <v>79596</v>
+        <v>78482</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16253,20 +16265,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -16281,10 +16293,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>465087</v>
+        <v>465002</v>
       </c>
       <c r="R154" t="n">
-        <v>6822688</v>
+        <v>6823138</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16343,10 +16355,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>117711658</v>
+        <v>117711875</v>
       </c>
       <c r="B155" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16359,21 +16371,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16383,10 +16395,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>464989</v>
+        <v>464916</v>
       </c>
       <c r="R155" t="n">
-        <v>6823212</v>
+        <v>6823144</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16445,10 +16457,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>117711845</v>
+        <v>117711991</v>
       </c>
       <c r="B156" t="n">
-        <v>78480</v>
+        <v>78127</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16461,21 +16473,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16485,10 +16497,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>465139</v>
+        <v>465046</v>
       </c>
       <c r="R156" t="n">
-        <v>6822785</v>
+        <v>6823084</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16547,10 +16559,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>117711906</v>
+        <v>117711397</v>
       </c>
       <c r="B157" t="n">
-        <v>78480</v>
+        <v>78516</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16563,21 +16575,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16587,10 +16599,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>465048</v>
+        <v>465229</v>
       </c>
       <c r="R157" t="n">
-        <v>6822878</v>
+        <v>6822789</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16649,10 +16661,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>117711826</v>
+        <v>117711851</v>
       </c>
       <c r="B158" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16689,10 +16701,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>465192</v>
+        <v>465136</v>
       </c>
       <c r="R158" t="n">
-        <v>6822668</v>
+        <v>6822847</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16751,10 +16763,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>117711908</v>
+        <v>117711565</v>
       </c>
       <c r="B159" t="n">
-        <v>78480</v>
+        <v>79592</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16763,38 +16775,41 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>465045</v>
+        <v>465115</v>
       </c>
       <c r="R159" t="n">
-        <v>6822855</v>
+        <v>6822797</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16829,12 +16844,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -16853,10 +16874,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>117711873</v>
+        <v>117712007</v>
       </c>
       <c r="B160" t="n">
-        <v>78480</v>
+        <v>79598</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16865,20 +16886,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -16893,10 +16914,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>464912</v>
+        <v>465087</v>
       </c>
       <c r="R160" t="n">
-        <v>6823140</v>
+        <v>6822688</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16955,10 +16976,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>117711407</v>
+        <v>117711842</v>
       </c>
       <c r="B161" t="n">
-        <v>78514</v>
+        <v>78482</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -16971,21 +16992,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16995,10 +17016,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>465007</v>
+        <v>465106</v>
       </c>
       <c r="R161" t="n">
-        <v>6823041</v>
+        <v>6822702</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17057,10 +17078,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>117711786</v>
+        <v>117711847</v>
       </c>
       <c r="B162" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17097,10 +17118,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>465086</v>
+        <v>465136</v>
       </c>
       <c r="R162" t="n">
-        <v>6823030</v>
+        <v>6822815</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17159,10 +17180,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>117711884</v>
+        <v>117711853</v>
       </c>
       <c r="B163" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17199,10 +17220,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>465002</v>
+        <v>465129</v>
       </c>
       <c r="R163" t="n">
-        <v>6823138</v>
+        <v>6822859</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17261,10 +17282,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>117711740</v>
+        <v>117711711</v>
       </c>
       <c r="B164" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17277,21 +17298,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17301,10 +17322,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>465415</v>
+        <v>465071</v>
       </c>
       <c r="R164" t="n">
-        <v>6822567</v>
+        <v>6822963</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17363,10 +17384,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>117711850</v>
+        <v>117711898</v>
       </c>
       <c r="B165" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17403,10 +17424,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>465139</v>
+        <v>465000</v>
       </c>
       <c r="R165" t="n">
-        <v>6822842</v>
+        <v>6822960</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17465,10 +17486,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>117711900</v>
+        <v>117711584</v>
       </c>
       <c r="B166" t="n">
-        <v>78480</v>
+        <v>79564</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17481,21 +17502,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17505,10 +17526,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>465014</v>
+        <v>464971</v>
       </c>
       <c r="R166" t="n">
-        <v>6822962</v>
+        <v>6823086</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17567,10 +17588,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>117711565</v>
+        <v>117711492</v>
       </c>
       <c r="B167" t="n">
-        <v>79590</v>
+        <v>79100</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17579,41 +17600,38 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>465115</v>
+        <v>465025</v>
       </c>
       <c r="R167" t="n">
-        <v>6822797</v>
+        <v>6822860</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17648,18 +17666,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -17678,10 +17690,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>117711700</v>
+        <v>117711740</v>
       </c>
       <c r="B168" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17694,21 +17706,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17718,10 +17730,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>465104</v>
+        <v>465415</v>
       </c>
       <c r="R168" t="n">
-        <v>6823045</v>
+        <v>6822567</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17780,10 +17792,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>117711467</v>
+        <v>117711920</v>
       </c>
       <c r="B169" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17796,21 +17808,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17820,10 +17832,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>465057</v>
+        <v>465088</v>
       </c>
       <c r="R169" t="n">
-        <v>6822708</v>
+        <v>6822770</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17882,10 +17894,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>117711564</v>
+        <v>117711658</v>
       </c>
       <c r="B170" t="n">
-        <v>79590</v>
+        <v>78219</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17894,41 +17906,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>465043</v>
+        <v>464989</v>
       </c>
       <c r="R170" t="n">
-        <v>6822864</v>
+        <v>6823212</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17963,18 +17972,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -17993,10 +17996,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>117711994</v>
+        <v>117711473</v>
       </c>
       <c r="B171" t="n">
-        <v>78125</v>
+        <v>79100</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18009,21 +18012,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18033,10 +18036,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>465054</v>
+        <v>465065</v>
       </c>
       <c r="R171" t="n">
-        <v>6823006</v>
+        <v>6822969</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18095,10 +18098,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>117711763</v>
+        <v>117711564</v>
       </c>
       <c r="B172" t="n">
-        <v>78480</v>
+        <v>79592</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18107,38 +18110,41 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>465048</v>
+        <v>465043</v>
       </c>
       <c r="R172" t="n">
-        <v>6822660</v>
+        <v>6822864</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18173,12 +18179,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -18197,10 +18209,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>117711653</v>
+        <v>117711478</v>
       </c>
       <c r="B173" t="n">
-        <v>78217</v>
+        <v>79100</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18213,21 +18225,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18237,10 +18249,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>465082</v>
+        <v>464943</v>
       </c>
       <c r="R173" t="n">
-        <v>6823073</v>
+        <v>6823108</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18299,10 +18311,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>117711789</v>
+        <v>117711609</v>
       </c>
       <c r="B174" t="n">
-        <v>78480</v>
+        <v>78508</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18311,25 +18323,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18339,10 +18351,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>465120</v>
+        <v>465379</v>
       </c>
       <c r="R174" t="n">
-        <v>6823039</v>
+        <v>6822539</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18401,10 +18413,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>117711924</v>
+        <v>117711766</v>
       </c>
       <c r="B175" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18441,10 +18453,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>465032</v>
+        <v>465122</v>
       </c>
       <c r="R175" t="n">
-        <v>6822777</v>
+        <v>6822673</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18503,10 +18515,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>117711775</v>
+        <v>117711785</v>
       </c>
       <c r="B176" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18543,10 +18555,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>465240</v>
+        <v>465096</v>
       </c>
       <c r="R176" t="n">
-        <v>6822759</v>
+        <v>6823017</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18605,10 +18617,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>117711833</v>
+        <v>117711475</v>
       </c>
       <c r="B177" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18621,21 +18633,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18645,10 +18657,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>465310</v>
+        <v>465003</v>
       </c>
       <c r="R177" t="n">
-        <v>6822472</v>
+        <v>6823040</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18707,10 +18719,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>117711820</v>
+        <v>117711566</v>
       </c>
       <c r="B178" t="n">
-        <v>78480</v>
+        <v>79592</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18719,38 +18731,41 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>465186</v>
+        <v>465130</v>
       </c>
       <c r="R178" t="n">
-        <v>6822793</v>
+        <v>6822768</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18785,12 +18800,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -18809,10 +18830,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>117711893</v>
+        <v>117711710</v>
       </c>
       <c r="B179" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18825,21 +18846,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18849,10 +18870,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>465052</v>
+        <v>465058</v>
       </c>
       <c r="R179" t="n">
-        <v>6823002</v>
+        <v>6822707</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18911,10 +18932,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>117711710</v>
+        <v>117711918</v>
       </c>
       <c r="B180" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18927,21 +18948,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18951,10 +18972,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>465058</v>
+        <v>465083</v>
       </c>
       <c r="R180" t="n">
-        <v>6822707</v>
+        <v>6822781</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19013,10 +19034,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>117711610</v>
+        <v>117711672</v>
       </c>
       <c r="B181" t="n">
-        <v>78506</v>
+        <v>96799</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19029,21 +19050,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6434</v>
+        <v>221941</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19053,10 +19074,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>465212</v>
+        <v>464987</v>
       </c>
       <c r="R181" t="n">
-        <v>6822555</v>
+        <v>6823079</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19115,10 +19136,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>117711459</v>
+        <v>117711394</v>
       </c>
       <c r="B182" t="n">
-        <v>79098</v>
+        <v>78516</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19131,21 +19152,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19155,10 +19176,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>465193</v>
+        <v>465395</v>
       </c>
       <c r="R182" t="n">
-        <v>6822569</v>
+        <v>6822489</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19217,10 +19238,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>117711563</v>
+        <v>117711653</v>
       </c>
       <c r="B183" t="n">
-        <v>79590</v>
+        <v>78219</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19229,41 +19250,38 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>465121</v>
+        <v>465082</v>
       </c>
       <c r="R183" t="n">
-        <v>6822755</v>
+        <v>6823073</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19298,18 +19316,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD183" t="b">
         <v>0</v>
       </c>
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -19328,10 +19340,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>117711851</v>
+        <v>117711763</v>
       </c>
       <c r="B184" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19368,10 +19380,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>465136</v>
+        <v>465048</v>
       </c>
       <c r="R184" t="n">
-        <v>6822847</v>
+        <v>6822660</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19430,10 +19442,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>117711898</v>
+        <v>117711906</v>
       </c>
       <c r="B185" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19470,10 +19482,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>465000</v>
+        <v>465048</v>
       </c>
       <c r="R185" t="n">
-        <v>6822960</v>
+        <v>6822878</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19532,10 +19544,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>117711772</v>
+        <v>117711777</v>
       </c>
       <c r="B186" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19572,10 +19584,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>465258</v>
+        <v>465234</v>
       </c>
       <c r="R186" t="n">
-        <v>6822696</v>
+        <v>6822786</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19634,10 +19646,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>117711770</v>
+        <v>117711886</v>
       </c>
       <c r="B187" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19674,10 +19686,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>465340</v>
+        <v>465028</v>
       </c>
       <c r="R187" t="n">
-        <v>6822636</v>
+        <v>6823123</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19736,10 +19748,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>117711543</v>
+        <v>117711775</v>
       </c>
       <c r="B188" t="n">
-        <v>56499</v>
+        <v>78482</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19748,50 +19760,38 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>465107</v>
+        <v>465240</v>
       </c>
       <c r="R188" t="n">
-        <v>6822869</v>
+        <v>6822759</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19850,10 +19850,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>117711652</v>
+        <v>117711900</v>
       </c>
       <c r="B189" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19866,21 +19866,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19890,10 +19890,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>465407</v>
+        <v>465014</v>
       </c>
       <c r="R189" t="n">
-        <v>6822454</v>
+        <v>6822962</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19952,10 +19952,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>117711397</v>
+        <v>117711472</v>
       </c>
       <c r="B190" t="n">
-        <v>78514</v>
+        <v>79100</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -19968,21 +19968,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19992,10 +19992,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>465229</v>
+        <v>465070</v>
       </c>
       <c r="R190" t="n">
-        <v>6822789</v>
+        <v>6822961</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20054,10 +20054,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>117711396</v>
+        <v>117711820</v>
       </c>
       <c r="B191" t="n">
-        <v>78514</v>
+        <v>78482</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20070,21 +20070,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20094,10 +20094,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>465249</v>
+        <v>465186</v>
       </c>
       <c r="R191" t="n">
-        <v>6822748</v>
+        <v>6822793</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20156,10 +20156,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>117711479</v>
+        <v>117711878</v>
       </c>
       <c r="B192" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20172,21 +20172,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20196,10 +20196,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>464928</v>
+        <v>464955</v>
       </c>
       <c r="R192" t="n">
-        <v>6823159</v>
+        <v>6823167</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20258,10 +20258,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>117711821</v>
+        <v>117711891</v>
       </c>
       <c r="B193" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20298,10 +20298,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>465185</v>
+        <v>465027</v>
       </c>
       <c r="R193" t="n">
-        <v>6822757</v>
+        <v>6823022</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20360,10 +20360,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>117711620</v>
+        <v>117711730</v>
       </c>
       <c r="B194" t="n">
-        <v>79589</v>
+        <v>90650</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20372,25 +20372,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6461</v>
+        <v>1503</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20400,10 +20400,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>465060</v>
+        <v>465146</v>
       </c>
       <c r="R194" t="n">
-        <v>6822839</v>
+        <v>6822800</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20462,10 +20462,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>117711618</v>
+        <v>117711404</v>
       </c>
       <c r="B195" t="n">
-        <v>79589</v>
+        <v>78516</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20474,25 +20474,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6461</v>
+        <v>185</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20502,10 +20502,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>465010</v>
+        <v>465098</v>
       </c>
       <c r="R195" t="n">
-        <v>6823041</v>
+        <v>6822909</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20564,10 +20564,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>117711439</v>
+        <v>117711402</v>
       </c>
       <c r="B196" t="n">
-        <v>79098</v>
+        <v>78516</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20580,21 +20580,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20604,10 +20604,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>465238</v>
+        <v>465170</v>
       </c>
       <c r="R196" t="n">
-        <v>6822512</v>
+        <v>6822729</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20666,10 +20666,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>117711485</v>
+        <v>117711907</v>
       </c>
       <c r="B197" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20682,21 +20682,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20709,7 +20709,7 @@
         <v>465022</v>
       </c>
       <c r="R197" t="n">
-        <v>6823158</v>
+        <v>6822851</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20768,10 +20768,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>117711878</v>
+        <v>117711440</v>
       </c>
       <c r="B198" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20784,21 +20784,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20808,10 +20808,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>464955</v>
+        <v>465352</v>
       </c>
       <c r="R198" t="n">
-        <v>6823167</v>
+        <v>6822592</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20870,10 +20870,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>117711931</v>
+        <v>117711770</v>
       </c>
       <c r="B199" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -20910,10 +20910,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>464993</v>
+        <v>465340</v>
       </c>
       <c r="R199" t="n">
-        <v>6822829</v>
+        <v>6822636</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20972,10 +20972,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>117711856</v>
+        <v>117711788</v>
       </c>
       <c r="B200" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21012,10 +21012,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>465118</v>
+        <v>465095</v>
       </c>
       <c r="R200" t="n">
-        <v>6822876</v>
+        <v>6823035</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21074,10 +21074,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>117711830</v>
+        <v>117711995</v>
       </c>
       <c r="B201" t="n">
-        <v>78480</v>
+        <v>78127</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21090,21 +21090,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21114,10 +21114,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>465282</v>
+        <v>465043</v>
       </c>
       <c r="R201" t="n">
-        <v>6822525</v>
+        <v>6822986</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21176,10 +21176,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>117711848</v>
+        <v>117712005</v>
       </c>
       <c r="B202" t="n">
-        <v>78480</v>
+        <v>91774</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21188,25 +21188,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21216,10 +21216,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>465126</v>
+        <v>465040</v>
       </c>
       <c r="R202" t="n">
-        <v>6822829</v>
+        <v>6822725</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21278,10 +21278,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>117711882</v>
+        <v>117711771</v>
       </c>
       <c r="B203" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21318,10 +21318,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>465023</v>
+        <v>465314</v>
       </c>
       <c r="R203" t="n">
-        <v>6823173</v>
+        <v>6822659</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21380,10 +21380,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>117711461</v>
+        <v>117711931</v>
       </c>
       <c r="B204" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21396,21 +21396,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21420,10 +21420,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>465276</v>
+        <v>464993</v>
       </c>
       <c r="R204" t="n">
-        <v>6822556</v>
+        <v>6822829</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21482,10 +21482,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>117711608</v>
+        <v>117711825</v>
       </c>
       <c r="B205" t="n">
-        <v>78506</v>
+        <v>78482</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21494,25 +21494,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21522,10 +21522,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>465207</v>
+        <v>465178</v>
       </c>
       <c r="R205" t="n">
-        <v>6822564</v>
+        <v>6822682</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21584,10 +21584,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>117711406</v>
+        <v>117711831</v>
       </c>
       <c r="B206" t="n">
-        <v>78514</v>
+        <v>78482</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21600,21 +21600,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21624,10 +21624,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>465008</v>
+        <v>465280</v>
       </c>
       <c r="R206" t="n">
-        <v>6823044</v>
+        <v>6822526</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21686,10 +21686,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>117711895</v>
+        <v>117711912</v>
       </c>
       <c r="B207" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -21726,10 +21726,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>465019</v>
+        <v>465072</v>
       </c>
       <c r="R207" t="n">
-        <v>6822976</v>
+        <v>6822834</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21788,10 +21788,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>117711872</v>
+        <v>117711789</v>
       </c>
       <c r="B208" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21828,10 +21828,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>464915</v>
+        <v>465120</v>
       </c>
       <c r="R208" t="n">
-        <v>6823136</v>
+        <v>6823039</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21890,10 +21890,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>117711913</v>
+        <v>117711618</v>
       </c>
       <c r="B209" t="n">
-        <v>78480</v>
+        <v>79591</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -21902,25 +21902,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -21930,10 +21930,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>465106</v>
+        <v>465010</v>
       </c>
       <c r="R209" t="n">
-        <v>6822818</v>
+        <v>6823041</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21992,10 +21992,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>117711696</v>
+        <v>117711408</v>
       </c>
       <c r="B210" t="n">
-        <v>78216</v>
+        <v>78516</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22008,21 +22008,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -22032,10 +22032,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>465187</v>
+        <v>465002</v>
       </c>
       <c r="R210" t="n">
-        <v>6822623</v>
+        <v>6823046</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22094,10 +22094,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>117711659</v>
+        <v>117711651</v>
       </c>
       <c r="B211" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22134,10 +22134,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>465007</v>
+        <v>465187</v>
       </c>
       <c r="R211" t="n">
-        <v>6823134</v>
+        <v>6822613</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22199,7 +22199,7 @@
         <v>117711581</v>
       </c>
       <c r="B212" t="n">
-        <v>74590</v>
+        <v>74592</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>

--- a/artfynd/A 47952-2023 artfynd.xlsx
+++ b/artfynd/A 47952-2023 artfynd.xlsx
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117711659</v>
+        <v>117711734</v>
       </c>
       <c r="B17" t="n">
-        <v>78219</v>
+        <v>90519</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,34 +2230,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465007</v>
+        <v>465126</v>
       </c>
       <c r="R17" t="n">
-        <v>6823134</v>
+        <v>6822834</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2292,12 +2295,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Mitt i planerad körväg</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2316,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117711662</v>
+        <v>117711586</v>
       </c>
       <c r="B18" t="n">
-        <v>78219</v>
+        <v>79564</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2341,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465042</v>
+        <v>465034</v>
       </c>
       <c r="R18" t="n">
-        <v>6822770</v>
+        <v>6822859</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117711734</v>
+        <v>117711659</v>
       </c>
       <c r="B19" t="n">
-        <v>90519</v>
+        <v>78219</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,37 +2443,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465126</v>
+        <v>465007</v>
       </c>
       <c r="R19" t="n">
-        <v>6822834</v>
+        <v>6823134</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2499,18 +2505,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mitt i planerad körväg</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2529,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117711586</v>
+        <v>117711662</v>
       </c>
       <c r="B20" t="n">
-        <v>79564</v>
+        <v>78219</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2545,21 +2545,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465034</v>
+        <v>465042</v>
       </c>
       <c r="R20" t="n">
-        <v>6822859</v>
+        <v>6822770</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -8178,10 +8178,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117711699</v>
+        <v>117711916</v>
       </c>
       <c r="B75" t="n">
-        <v>78218</v>
+        <v>78482</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8194,21 +8194,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465258</v>
+        <v>465096</v>
       </c>
       <c r="R75" t="n">
-        <v>6822743</v>
+        <v>6822795</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8280,10 +8280,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117711916</v>
+        <v>117711612</v>
       </c>
       <c r="B76" t="n">
-        <v>78482</v>
+        <v>78508</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8292,25 +8292,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8320,10 +8320,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465096</v>
+        <v>465019</v>
       </c>
       <c r="R76" t="n">
-        <v>6822795</v>
+        <v>6822780</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8382,7 +8382,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117711823</v>
+        <v>117711856</v>
       </c>
       <c r="B77" t="n">
         <v>78482</v>
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465157</v>
+        <v>465118</v>
       </c>
       <c r="R77" t="n">
-        <v>6822719</v>
+        <v>6822876</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8484,10 +8484,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117711612</v>
+        <v>117711700</v>
       </c>
       <c r="B78" t="n">
-        <v>78508</v>
+        <v>78218</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8496,25 +8496,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8524,10 +8524,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>465019</v>
+        <v>465104</v>
       </c>
       <c r="R78" t="n">
-        <v>6822780</v>
+        <v>6823045</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8586,7 +8586,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117711856</v>
+        <v>117711850</v>
       </c>
       <c r="B79" t="n">
         <v>78482</v>
@@ -8626,10 +8626,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465118</v>
+        <v>465139</v>
       </c>
       <c r="R79" t="n">
-        <v>6822876</v>
+        <v>6822842</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8688,10 +8688,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117711700</v>
+        <v>117711909</v>
       </c>
       <c r="B80" t="n">
-        <v>78218</v>
+        <v>78482</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8704,21 +8704,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8728,10 +8728,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465104</v>
+        <v>465054</v>
       </c>
       <c r="R80" t="n">
-        <v>6823045</v>
+        <v>6822855</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8790,7 +8790,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117711850</v>
+        <v>117711915</v>
       </c>
       <c r="B81" t="n">
         <v>78482</v>
@@ -8830,10 +8830,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465139</v>
+        <v>465102</v>
       </c>
       <c r="R81" t="n">
-        <v>6822842</v>
+        <v>6822788</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8892,10 +8892,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117711909</v>
+        <v>117711699</v>
       </c>
       <c r="B82" t="n">
-        <v>78482</v>
+        <v>78218</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8908,21 +8908,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>465054</v>
+        <v>465258</v>
       </c>
       <c r="R82" t="n">
-        <v>6822855</v>
+        <v>6822743</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8994,7 +8994,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117711915</v>
+        <v>117711823</v>
       </c>
       <c r="B83" t="n">
         <v>78482</v>
@@ -9034,10 +9034,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>465102</v>
+        <v>465157</v>
       </c>
       <c r="R83" t="n">
-        <v>6822788</v>
+        <v>6822719</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11655,10 +11655,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>117711897</v>
+        <v>117711462</v>
       </c>
       <c r="B109" t="n">
-        <v>78482</v>
+        <v>79100</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11671,21 +11671,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>465002</v>
+        <v>465290</v>
       </c>
       <c r="R109" t="n">
-        <v>6822972</v>
+        <v>6822535</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11757,7 +11757,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>117711483</v>
+        <v>117711480</v>
       </c>
       <c r="B110" t="n">
         <v>79100</v>
@@ -11797,10 +11797,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464993</v>
+        <v>464969</v>
       </c>
       <c r="R110" t="n">
-        <v>6823209</v>
+        <v>6823166</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11859,7 +11859,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>117711881</v>
+        <v>117711897</v>
       </c>
       <c r="B111" t="n">
         <v>78482</v>
@@ -11899,10 +11899,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>465010</v>
+        <v>465002</v>
       </c>
       <c r="R111" t="n">
-        <v>6823186</v>
+        <v>6822972</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11961,10 +11961,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>117711829</v>
+        <v>117711483</v>
       </c>
       <c r="B112" t="n">
-        <v>78482</v>
+        <v>79100</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11977,21 +11977,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12001,10 +12001,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465274</v>
+        <v>464993</v>
       </c>
       <c r="R112" t="n">
-        <v>6822528</v>
+        <v>6823209</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12063,10 +12063,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>117711462</v>
+        <v>117711881</v>
       </c>
       <c r="B113" t="n">
-        <v>79100</v>
+        <v>78482</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12079,21 +12079,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12103,10 +12103,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>465290</v>
+        <v>465010</v>
       </c>
       <c r="R113" t="n">
-        <v>6822535</v>
+        <v>6823186</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12165,10 +12165,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>117711480</v>
+        <v>117711829</v>
       </c>
       <c r="B114" t="n">
-        <v>79100</v>
+        <v>78482</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12181,21 +12181,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464969</v>
+        <v>465274</v>
       </c>
       <c r="R114" t="n">
-        <v>6823166</v>
+        <v>6822528</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12267,10 +12267,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>117711732</v>
+        <v>117711407</v>
       </c>
       <c r="B115" t="n">
-        <v>79608</v>
+        <v>78516</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12283,21 +12283,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229504</v>
+        <v>185</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12307,10 +12307,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>465042</v>
+        <v>465007</v>
       </c>
       <c r="R115" t="n">
-        <v>6822859</v>
+        <v>6823041</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12369,10 +12369,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>117711407</v>
+        <v>117711732</v>
       </c>
       <c r="B116" t="n">
-        <v>78516</v>
+        <v>79608</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12385,21 +12385,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>185</v>
+        <v>229504</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12409,10 +12409,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>465007</v>
+        <v>465042</v>
       </c>
       <c r="R116" t="n">
-        <v>6823041</v>
+        <v>6822859</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14519,10 +14519,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>117711861</v>
+        <v>117711458</v>
       </c>
       <c r="B137" t="n">
-        <v>78482</v>
+        <v>79100</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14535,21 +14535,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14559,10 +14559,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>465018</v>
+        <v>465184</v>
       </c>
       <c r="R137" t="n">
-        <v>6823007</v>
+        <v>6822626</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14621,10 +14621,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>117711479</v>
+        <v>117711772</v>
       </c>
       <c r="B138" t="n">
-        <v>79100</v>
+        <v>78482</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14637,21 +14637,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14661,10 +14661,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464928</v>
+        <v>465258</v>
       </c>
       <c r="R138" t="n">
-        <v>6823159</v>
+        <v>6822696</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14723,10 +14723,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>117711458</v>
+        <v>117711765</v>
       </c>
       <c r="B139" t="n">
-        <v>79100</v>
+        <v>78482</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14739,21 +14739,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14763,10 +14763,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>465184</v>
+        <v>465105</v>
       </c>
       <c r="R139" t="n">
-        <v>6822626</v>
+        <v>6822680</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14825,10 +14825,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>117711772</v>
+        <v>117711482</v>
       </c>
       <c r="B140" t="n">
-        <v>78482</v>
+        <v>79100</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14841,21 +14841,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14865,10 +14865,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>465258</v>
+        <v>464989</v>
       </c>
       <c r="R140" t="n">
-        <v>6822696</v>
+        <v>6823223</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14927,7 +14927,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>117711765</v>
+        <v>117711889</v>
       </c>
       <c r="B141" t="n">
         <v>78482</v>
@@ -14967,10 +14967,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>465105</v>
+        <v>465072</v>
       </c>
       <c r="R141" t="n">
-        <v>6822680</v>
+        <v>6823099</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15029,10 +15029,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>117711482</v>
+        <v>117711861</v>
       </c>
       <c r="B142" t="n">
-        <v>79100</v>
+        <v>78482</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15045,21 +15045,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15069,10 +15069,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464989</v>
+        <v>465018</v>
       </c>
       <c r="R142" t="n">
-        <v>6823223</v>
+        <v>6823007</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15131,10 +15131,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>117711882</v>
+        <v>117711479</v>
       </c>
       <c r="B143" t="n">
-        <v>78482</v>
+        <v>79100</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15147,21 +15147,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15171,10 +15171,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>465023</v>
+        <v>464928</v>
       </c>
       <c r="R143" t="n">
-        <v>6823173</v>
+        <v>6823159</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15233,10 +15233,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>117711889</v>
+        <v>117711731</v>
       </c>
       <c r="B144" t="n">
-        <v>78482</v>
+        <v>90650</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15245,25 +15245,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15273,10 +15273,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>465072</v>
+        <v>465012</v>
       </c>
       <c r="R144" t="n">
-        <v>6823099</v>
+        <v>6823041</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15335,10 +15335,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>117711731</v>
+        <v>117711882</v>
       </c>
       <c r="B145" t="n">
-        <v>90650</v>
+        <v>78482</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15347,25 +15347,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>465012</v>
+        <v>465023</v>
       </c>
       <c r="R145" t="n">
-        <v>6823041</v>
+        <v>6823173</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16559,10 +16559,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>117711397</v>
+        <v>117711584</v>
       </c>
       <c r="B157" t="n">
-        <v>78516</v>
+        <v>79564</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16575,21 +16575,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16599,10 +16599,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>465229</v>
+        <v>464971</v>
       </c>
       <c r="R157" t="n">
-        <v>6822789</v>
+        <v>6823086</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17486,10 +17486,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>117711584</v>
+        <v>117711492</v>
       </c>
       <c r="B166" t="n">
-        <v>79564</v>
+        <v>79100</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17502,21 +17502,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17526,10 +17526,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>464971</v>
+        <v>465025</v>
       </c>
       <c r="R166" t="n">
-        <v>6823086</v>
+        <v>6822860</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17588,10 +17588,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>117711492</v>
+        <v>117711740</v>
       </c>
       <c r="B167" t="n">
-        <v>79100</v>
+        <v>78482</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17604,21 +17604,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17628,10 +17628,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>465025</v>
+        <v>465415</v>
       </c>
       <c r="R167" t="n">
-        <v>6822860</v>
+        <v>6822567</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17690,7 +17690,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>117711740</v>
+        <v>117711920</v>
       </c>
       <c r="B168" t="n">
         <v>78482</v>
@@ -17730,10 +17730,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>465415</v>
+        <v>465088</v>
       </c>
       <c r="R168" t="n">
-        <v>6822567</v>
+        <v>6822770</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17792,10 +17792,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>117711920</v>
+        <v>117711397</v>
       </c>
       <c r="B169" t="n">
-        <v>78482</v>
+        <v>78516</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17808,21 +17808,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17832,10 +17832,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>465088</v>
+        <v>465229</v>
       </c>
       <c r="R169" t="n">
-        <v>6822770</v>
+        <v>6822789</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19340,10 +19340,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>117711763</v>
+        <v>117711404</v>
       </c>
       <c r="B184" t="n">
-        <v>78482</v>
+        <v>78516</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19356,21 +19356,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19380,10 +19380,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>465048</v>
+        <v>465098</v>
       </c>
       <c r="R184" t="n">
-        <v>6822660</v>
+        <v>6822909</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19442,7 +19442,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>117711906</v>
+        <v>117711763</v>
       </c>
       <c r="B185" t="n">
         <v>78482</v>
@@ -19485,7 +19485,7 @@
         <v>465048</v>
       </c>
       <c r="R185" t="n">
-        <v>6822878</v>
+        <v>6822660</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19544,7 +19544,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>117711777</v>
+        <v>117711906</v>
       </c>
       <c r="B186" t="n">
         <v>78482</v>
@@ -19584,10 +19584,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>465234</v>
+        <v>465048</v>
       </c>
       <c r="R186" t="n">
-        <v>6822786</v>
+        <v>6822878</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19646,7 +19646,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>117711886</v>
+        <v>117711777</v>
       </c>
       <c r="B187" t="n">
         <v>78482</v>
@@ -19686,10 +19686,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>465028</v>
+        <v>465234</v>
       </c>
       <c r="R187" t="n">
-        <v>6823123</v>
+        <v>6822786</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19748,7 +19748,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>117711775</v>
+        <v>117711886</v>
       </c>
       <c r="B188" t="n">
         <v>78482</v>
@@ -19788,10 +19788,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>465240</v>
+        <v>465028</v>
       </c>
       <c r="R188" t="n">
-        <v>6822759</v>
+        <v>6823123</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19850,7 +19850,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>117711900</v>
+        <v>117711775</v>
       </c>
       <c r="B189" t="n">
         <v>78482</v>
@@ -19890,10 +19890,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>465014</v>
+        <v>465240</v>
       </c>
       <c r="R189" t="n">
-        <v>6822962</v>
+        <v>6822759</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19952,10 +19952,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>117711472</v>
+        <v>117711900</v>
       </c>
       <c r="B190" t="n">
-        <v>79100</v>
+        <v>78482</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -19968,21 +19968,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19992,10 +19992,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>465070</v>
+        <v>465014</v>
       </c>
       <c r="R190" t="n">
-        <v>6822961</v>
+        <v>6822962</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20054,10 +20054,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>117711820</v>
+        <v>117711472</v>
       </c>
       <c r="B191" t="n">
-        <v>78482</v>
+        <v>79100</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20070,21 +20070,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20094,10 +20094,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>465186</v>
+        <v>465070</v>
       </c>
       <c r="R191" t="n">
-        <v>6822793</v>
+        <v>6822961</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20156,7 +20156,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>117711878</v>
+        <v>117711820</v>
       </c>
       <c r="B192" t="n">
         <v>78482</v>
@@ -20196,10 +20196,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>464955</v>
+        <v>465186</v>
       </c>
       <c r="R192" t="n">
-        <v>6823167</v>
+        <v>6822793</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20258,7 +20258,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>117711891</v>
+        <v>117711878</v>
       </c>
       <c r="B193" t="n">
         <v>78482</v>
@@ -20298,10 +20298,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>465027</v>
+        <v>464955</v>
       </c>
       <c r="R193" t="n">
-        <v>6823022</v>
+        <v>6823167</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20360,10 +20360,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>117711730</v>
+        <v>117711891</v>
       </c>
       <c r="B194" t="n">
-        <v>90650</v>
+        <v>78482</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20372,25 +20372,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20400,10 +20400,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>465146</v>
+        <v>465027</v>
       </c>
       <c r="R194" t="n">
-        <v>6822800</v>
+        <v>6823022</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20462,10 +20462,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>117711404</v>
+        <v>117711730</v>
       </c>
       <c r="B195" t="n">
-        <v>78516</v>
+        <v>90650</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20474,25 +20474,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>185</v>
+        <v>1503</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20502,10 +20502,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>465098</v>
+        <v>465146</v>
       </c>
       <c r="R195" t="n">
-        <v>6822909</v>
+        <v>6822800</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>

--- a/artfynd/A 47952-2023 artfynd.xlsx
+++ b/artfynd/A 47952-2023 artfynd.xlsx
@@ -22302,10 +22302,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119549060</v>
+        <v>119549064</v>
       </c>
       <c r="B213" t="n">
-        <v>91884</v>
+        <v>78263</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22318,21 +22318,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22342,10 +22342,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>465204</v>
+        <v>465408</v>
       </c>
       <c r="R213" t="n">
-        <v>6822558</v>
+        <v>6822453</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22404,10 +22404,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119549075</v>
+        <v>119549060</v>
       </c>
       <c r="B214" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22416,47 +22416,38 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>465064</v>
+        <v>465204</v>
       </c>
       <c r="R214" t="n">
-        <v>6823050</v>
+        <v>6822558</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22617,10 +22608,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119549064</v>
+        <v>119549075</v>
       </c>
       <c r="B216" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22629,38 +22620,47 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>465408</v>
+        <v>465064</v>
       </c>
       <c r="R216" t="n">
-        <v>6822453</v>
+        <v>6823050</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>

--- a/artfynd/A 47952-2023 artfynd.xlsx
+++ b/artfynd/A 47952-2023 artfynd.xlsx
@@ -22302,10 +22302,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119549064</v>
+        <v>119549080</v>
       </c>
       <c r="B213" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22314,25 +22314,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22342,10 +22342,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>465408</v>
+        <v>465375</v>
       </c>
       <c r="R213" t="n">
-        <v>6822453</v>
+        <v>6822455</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22506,10 +22506,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119549080</v>
+        <v>119549064</v>
       </c>
       <c r="B215" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22518,25 +22518,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22546,10 +22546,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>465375</v>
+        <v>465408</v>
       </c>
       <c r="R215" t="n">
-        <v>6822455</v>
+        <v>6822453</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>

--- a/artfynd/A 47952-2023 artfynd.xlsx
+++ b/artfynd/A 47952-2023 artfynd.xlsx
@@ -13791,7 +13791,7 @@
         <v>117711537</v>
       </c>
       <c r="B130" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/artfynd/A 47952-2023 artfynd.xlsx
+++ b/artfynd/A 47952-2023 artfynd.xlsx
@@ -13791,7 +13791,7 @@
         <v>117711537</v>
       </c>
       <c r="B130" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/artfynd/A 47952-2023 artfynd.xlsx
+++ b/artfynd/A 47952-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY266"/>
+  <dimension ref="A1:AZ266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711394</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711396</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711397</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711402</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711403</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711404</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711405</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711406</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711407</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711408</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711409</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711410</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117700535</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711989</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711990</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2239,6 +2319,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711991</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2336,6 +2421,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711993</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2433,6 +2523,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711994</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2530,6 +2625,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711995</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2627,6 +2727,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117712006</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2739,6 +2844,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117700536</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2836,6 +2946,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711729</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2933,6 +3048,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711730</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3030,6 +3150,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711731</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3127,6 +3252,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711583</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3224,6 +3354,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711584</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3321,6 +3456,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711585</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3418,6 +3558,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711586</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3515,6 +3660,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711587</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3612,6 +3762,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117712003</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3709,6 +3864,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117712005</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3815,6 +3975,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549075</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3912,6 +4077,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549080</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4009,6 +4179,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117700534</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4115,6 +4290,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711735</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4221,6 +4401,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711736</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4318,6 +4503,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711738</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4415,6 +4605,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711739</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4512,6 +4707,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711740</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4609,6 +4809,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711759</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4706,6 +4911,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711761</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4803,6 +5013,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711762</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4900,6 +5115,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711763</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4997,6 +5217,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711764</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5094,6 +5319,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711765</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5191,6 +5421,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711766</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5288,6 +5523,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711767</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5385,6 +5625,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711768</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5482,6 +5727,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711769</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5579,6 +5829,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711770</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5676,6 +5931,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711771</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5773,6 +6033,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711772</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5870,6 +6135,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711773</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5967,6 +6237,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711775</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6064,6 +6339,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711777</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6161,6 +6441,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711778</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6258,6 +6543,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711779</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6355,6 +6645,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711781</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6452,6 +6747,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711785</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6549,6 +6849,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711786</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6646,6 +6951,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711788</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6743,6 +7053,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711789</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6840,6 +7155,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711792</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6937,6 +7257,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711819</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7034,6 +7359,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711820</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7131,6 +7461,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711821</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7228,6 +7563,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711822</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7325,6 +7665,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711823</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7422,6 +7767,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711824</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7519,6 +7869,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711825</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7616,6 +7971,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711826</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7713,6 +8073,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711827</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7810,6 +8175,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711829</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7907,6 +8277,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711830</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8004,6 +8379,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711831</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8101,6 +8481,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711832</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8198,6 +8583,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711833</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8295,6 +8685,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711834</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8392,6 +8787,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711836</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8489,6 +8889,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711838</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8586,6 +8991,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711841</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8683,6 +9093,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711842</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8780,6 +9195,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711843</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8877,6 +9297,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711845</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8974,6 +9399,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711846</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9071,6 +9501,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711847</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9168,6 +9603,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711848</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9265,6 +9705,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711850</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9362,6 +9807,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711851</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9459,6 +9909,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711852</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9556,6 +10011,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711853</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9653,6 +10113,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711854</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9750,6 +10215,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711856</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9847,6 +10317,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711858</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9944,6 +10419,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711859</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10041,6 +10521,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711860</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10138,6 +10623,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711861</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10235,6 +10725,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711862</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10332,6 +10827,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711864</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10429,6 +10929,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711865</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10526,6 +11031,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711866</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10623,6 +11133,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711867</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10720,6 +11235,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711868</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10817,6 +11337,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711869</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10914,6 +11439,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711870</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11011,6 +11541,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711871</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11108,6 +11643,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711872</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11205,6 +11745,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711873</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11302,6 +11847,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711875</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11399,6 +11949,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711876</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11496,6 +12051,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711878</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11593,6 +12153,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711879</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11690,6 +12255,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711880</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11787,6 +12357,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711881</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11884,6 +12459,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711882</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11981,6 +12561,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711883</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12078,6 +12663,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711884</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12175,6 +12765,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711886</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12272,6 +12867,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711888</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12369,6 +12969,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711889</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12466,6 +13071,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711890</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12563,6 +13173,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711891</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12660,6 +13275,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711893</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12757,6 +13377,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711894</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12854,6 +13479,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711895</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12951,6 +13581,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711896</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13048,6 +13683,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711897</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13145,6 +13785,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711898</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13242,6 +13887,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711899</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13339,6 +13989,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711900</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13436,6 +14091,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711901</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13533,6 +14193,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711903</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13630,6 +14295,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711904</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13727,6 +14397,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711905</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13824,6 +14499,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711906</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13921,6 +14601,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711907</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14018,6 +14703,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711908</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14115,6 +14805,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711909</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14212,6 +14907,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711911</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14309,6 +15009,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711912</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14406,6 +15111,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711913</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14503,6 +15213,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711914</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14600,6 +15315,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711915</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14697,6 +15417,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711916</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14794,6 +15519,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711917</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14891,6 +15621,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711918</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -14988,6 +15723,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711919</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15085,6 +15825,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711920</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15182,6 +15927,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711922</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15279,6 +16029,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711923</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15376,6 +16131,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711924</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15473,6 +16233,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711925</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15570,6 +16335,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711926</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15667,6 +16437,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711927</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15764,6 +16539,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711928</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -15861,6 +16641,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711929</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -15958,6 +16743,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711930</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16055,6 +16845,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711931</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16152,6 +16947,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711932</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16249,6 +17049,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711933</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16346,6 +17151,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711938</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16443,6 +17253,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711939</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16540,6 +17355,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711941</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16637,6 +17457,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711608</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16734,6 +17559,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711609</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -16831,6 +17661,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711610</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -16928,6 +17763,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711611</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17025,6 +17865,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711612</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17122,6 +17967,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711383</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17219,6 +18069,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711384</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17316,6 +18171,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711385</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17413,6 +18273,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711696</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17510,6 +18375,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711697</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17607,6 +18477,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711698</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -17704,6 +18579,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711699</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -17801,6 +18681,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711700</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -17898,6 +18783,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711702</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -17995,6 +18885,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711708</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18092,6 +18987,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711710</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18189,6 +19089,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711711</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18286,6 +19191,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711712</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18383,6 +19293,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711713</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18480,6 +19395,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711715</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18577,6 +19497,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711716</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -18674,6 +19599,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711717</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -18771,6 +19701,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711416</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -18868,6 +19803,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711438</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -18965,6 +19905,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711439</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19062,6 +20007,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711440</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19159,6 +20109,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711441</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19256,6 +20211,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711443</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19353,6 +20313,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711444</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19450,6 +20415,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711445</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19547,6 +20517,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711458</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -19644,6 +20619,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711459</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -19741,6 +20721,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711460</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -19838,6 +20823,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711461</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -19935,6 +20925,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711462</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20032,6 +21027,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711463</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20129,6 +21129,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711467</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20226,6 +21231,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711468</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20323,6 +21333,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711470</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20420,6 +21435,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711471</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -20517,6 +21537,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711472</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -20614,6 +21639,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711473</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -20711,6 +21741,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711474</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -20808,6 +21843,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711475</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -20905,6 +21945,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711476</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21002,6 +22047,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711477</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21099,6 +22149,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711478</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21196,6 +22251,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711479</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21293,6 +22353,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711480</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21390,6 +22455,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711482</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -21487,6 +22557,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711483</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -21584,6 +22659,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711484</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -21681,6 +22761,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711485</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -21778,6 +22863,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711486</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -21875,6 +22965,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711487</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -21972,6 +23067,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711489</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22069,6 +23169,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711491</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22166,6 +23271,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711492</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22263,6 +23373,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711493</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -22360,6 +23475,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711494</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -22457,6 +23577,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711495</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -22554,6 +23679,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711674</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -22651,6 +23781,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711675</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -22757,6 +23892,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711677</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -22854,6 +23994,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711617</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -22951,6 +24096,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711618</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23048,6 +24198,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711619</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23145,6 +24300,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711620</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23242,6 +24402,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711621</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -23348,6 +24513,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711555</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -23454,6 +24624,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711562</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -23560,6 +24735,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711563</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -23666,6 +24846,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711564</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -23772,6 +24957,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711565</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -23878,6 +25068,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711566</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -23984,6 +25179,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711570</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24081,6 +25281,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117712007</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24182,6 +25387,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711581</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24287,6 +25497,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711537</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -24397,6 +25612,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711593</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -24507,6 +25727,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711594</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -24612,6 +25837,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711542</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -24721,6 +25951,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711543</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -24828,6 +26063,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711378</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -24925,6 +26165,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711672</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25022,6 +26267,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711625</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25119,6 +26369,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711651</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25216,6 +26471,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711652</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -25313,6 +26573,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711653</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -25410,6 +26675,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711654</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -25507,6 +26777,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711655</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -25604,6 +26879,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711656</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -25701,6 +26981,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711657</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -25798,6 +27083,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711658</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -25895,6 +27185,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711659</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -25992,6 +27287,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711660</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -26089,6 +27389,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711661</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -26186,6 +27491,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711662</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -26283,6 +27593,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549064</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -26380,6 +27695,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711732</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -26477,6 +27797,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711523</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -26574,8 +27899,280 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711525</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>